--- a/AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26.xlsx
+++ b/AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
   <si>
     <t xml:space="preserve">AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26 — SAE Aero 2026 Micro, guide §8.6</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">WHICH CELLS TO EDIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue-on-yellow cells in Row 1 of each sheet (E1..K1) are the only inputs; everything else is a formula.</t>
+    <t xml:space="preserve">Blue-on-yellow cells in Row 1 of each sheet (E1..L1) are the only inputs; everything else is a formula.</t>
   </si>
   <si>
     <t xml:space="preserve">Re-enter Row 1 from Tools ▸ Equations ▸ Value column whenever a tail global moves.</t>
@@ -54,6 +54,27 @@
   </si>
   <si>
     <t xml:space="preserve">Trailing edge is CLOSED: B3 and B133 are overridden to 0 (the raw file carries ±0.00126).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1 — THE EMPENNAGE VERTICAL DATUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The empennage is referenced to AX_Long_Emp, which sits y_emp_axis above AX_Long, so every sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carries L1 = y_emp_axis. For the HT this is its ONLY vertical datum — the stabiliser has none of its</t>
+  </si>
+  <si>
+    <t xml:space="preserve">own, and its chord plane lands at Y = y_emp_axis. For the VT, L1 is applied ON TOP OF K1 = h_tail_top,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is itself measured from the waterline, so the fin root ends up h_tail_top above the boom axis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the fin should root ON the boom instead, set L1 to 0 on the two VT sheets and give the fin its own</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y_VT_root global measured from AX_Long_Emp. Do not compensate by dropping L1 from the HT.</t>
   </si>
   <si>
     <t xml:space="preserve">INCIDENCE SENSE — READ BEFORE CHANGING F1</t>
@@ -113,6 +134,9 @@
     <t xml:space="preserve">    h_tail_top     = 35.789150</t>
   </si>
   <si>
+    <t xml:space="preserve">    y_emp_axis     = 25.000000</t>
+  </si>
+  <si>
     <t xml:space="preserve">HT root — NACA 0012</t>
   </si>
   <si>
@@ -144,6 +168,9 @@
   </si>
   <si>
     <t xml:space="preserve">J1 root-LE station [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1 empennage lift [mm]</t>
   </si>
   <si>
     <t xml:space="preserve">TE closed to 0 in B3 and B133 — see _README</t>
@@ -553,7 +580,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="114"/>
@@ -644,20 +671,20 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
+      <c r="A20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -682,38 +709,81 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -732,17 +802,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>176.426266456864</v>
@@ -762,37 +832,43 @@
       <c r="J1" s="3" t="n">
         <v>848.131927603976</v>
       </c>
+      <c r="L1" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,15 +883,15 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.15718790444588</v>
+        <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.1571879044459</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * COS(RADIANS($F$1)) - (B3 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
         <v>-1024.47758847485</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
+      <c r="N3" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -830,15 +906,15 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.39021192603294</v>
+        <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.3902119260329</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * COS(RADIANS($F$1)) - (B4 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
         <v>-1024.36635535396</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
+      <c r="N4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -853,8 +929,8 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.422634951324</v>
+        <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.422634951324</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * COS(RADIANS($F$1)) - (B5 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -873,8 +949,8 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.47646081144163</v>
+        <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.4764608114416</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * COS(RADIANS($F$1)) - (B6 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -893,8 +969,8 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.55120980751204</v>
+        <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.551209807512</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * COS(RADIANS($F$1)) - (B7 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -913,8 +989,8 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.64605576026466</v>
+        <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.6460557602647</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * COS(RADIANS($F$1)) - (B8 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -933,8 +1009,8 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.76071991836965</v>
+        <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.7607199183696</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * COS(RADIANS($F$1)) - (B9 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -953,8 +1029,8 @@
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.89406040809918</v>
+        <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.8940604080992</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * COS(RADIANS($F$1)) - (B10 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -973,8 +1049,8 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.04494767010125</v>
+        <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.0449476701012</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * COS(RADIANS($F$1)) - (B11 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -993,8 +1069,8 @@
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.21245309256778</v>
+        <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.2124530925678</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * COS(RADIANS($F$1)) - (B12 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1013,8 +1089,8 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.39530158329393</v>
+        <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.3953015832939</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * COS(RADIANS($F$1)) - (B13 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1033,8 +1109,8 @@
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.59223652163859</v>
+        <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.5922365216386</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * COS(RADIANS($F$1)) - (B14 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1053,8 +1129,8 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.80166096375175</v>
+        <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.8016609637517</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * COS(RADIANS($F$1)) - (B15 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1073,8 +1149,8 @@
         <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.02253155091204</v>
+        <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.022531550912</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * COS(RADIANS($F$1)) - (B16 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1093,8 +1169,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.25326981083319</v>
+        <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.2532698108332</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * COS(RADIANS($F$1)) - (B17 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1113,8 +1189,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.49233421435632</v>
+        <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.4923342143563</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * COS(RADIANS($F$1)) - (B18 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1133,8 +1209,8 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.73836570830283</v>
+        <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.7383657083028</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * COS(RADIANS($F$1)) - (B19 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1153,8 +1229,8 @@
         <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.98982276351385</v>
+        <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.9898227635139</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * COS(RADIANS($F$1)) - (B20 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1173,8 +1249,8 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.24502447516561</v>
+        <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.2450244751656</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * COS(RADIANS($F$1)) - (B21 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1193,8 +1269,8 @@
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.50281889481135</v>
+        <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.5028188948114</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * COS(RADIANS($F$1)) - (B22 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1213,8 +1289,8 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.76136111321076</v>
+        <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.7613611132108</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * COS(RADIANS($F$1)) - (B23 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1233,8 +1309,8 @@
         <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.0193474918764</v>
+        <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.0193474918764</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * COS(RADIANS($F$1)) - (B24 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1253,8 +1329,8 @@
         <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.2749515931316</v>
+        <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.2749515931316</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * COS(RADIANS($F$1)) - (B25 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1273,8 +1349,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.5270584116571</v>
+        <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.5270584116571</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * COS(RADIANS($F$1)) - (B26 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1293,8 +1369,8 @@
         <v>0</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.7736836625476</v>
+        <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.7736836625476</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * COS(RADIANS($F$1)) - (B27 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1313,8 +1389,8 @@
         <v>0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.0133904888387</v>
+        <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.0133904888387</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * COS(RADIANS($F$1)) - (B28 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1333,8 +1409,8 @@
         <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.2443709244174</v>
+        <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.2443709244174</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * COS(RADIANS($F$1)) - (B29 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1353,8 +1429,8 @@
         <v>0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.4651942695073</v>
+        <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.4651942695073</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * COS(RADIANS($F$1)) - (B30 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1373,8 +1449,8 @@
         <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.6737245491623</v>
+        <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.6737245491623</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * COS(RADIANS($F$1)) - (B31 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1393,8 +1469,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="5" t="n">
-        <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.8683670591894</v>
+        <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.8683670591894</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * COS(RADIANS($F$1)) - (B32 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1413,8 +1489,8 @@
         <v>0</v>
       </c>
       <c r="D33" s="5" t="n">
-        <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.0473323050392</v>
+        <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.0473323050393</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * COS(RADIANS($F$1)) - (B33 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1433,8 +1509,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="5" t="n">
-        <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.2085089405177</v>
+        <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.2085089405177</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * COS(RADIANS($F$1)) - (B34 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1453,8 +1529,8 @@
         <v>0</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.3501259426392</v>
+        <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.3501259426392</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * COS(RADIANS($F$1)) - (B35 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1473,8 +1549,8 @@
         <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.470229812438</v>
+        <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.470229812438</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * COS(RADIANS($F$1)) - (B36 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1493,8 +1569,8 @@
         <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.5667092037199</v>
+        <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.5667092037199</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * COS(RADIANS($F$1)) - (B37 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1513,8 +1589,8 @@
         <v>0</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6377869363114</v>
+        <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6377869363114</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * COS(RADIANS($F$1)) - (B38 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1533,8 +1609,8 @@
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6815218256228</v>
+        <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6815218256228</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * COS(RADIANS($F$1)) - (B39 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1553,8 +1629,8 @@
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6961366914805</v>
+        <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6961366914805</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * COS(RADIANS($F$1)) - (B40 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1573,8 +1649,8 @@
         <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6800368296915</v>
+        <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6800368296915</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * COS(RADIANS($F$1)) - (B41 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1593,8 +1669,8 @@
         <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6314512172704</v>
+        <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6314512172704</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1613,8 +1689,8 @@
         <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.5489368400647</v>
+        <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.5489368400647</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * COS(RADIANS($F$1)) - (B43 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1633,8 +1709,8 @@
         <v>0</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.4312393170902</v>
+        <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.4312393170902</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * COS(RADIANS($F$1)) - (B44 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1653,8 +1729,8 @@
         <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.2774445905715</v>
+        <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.2774445905716</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * COS(RADIANS($F$1)) - (B45 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1673,8 +1749,8 @@
         <v>0</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.0868149215257</v>
+        <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.0868149215257</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * COS(RADIANS($F$1)) - (B46 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1693,8 +1769,8 @@
         <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.8584239378015</v>
+        <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.8584239378015</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * COS(RADIANS($F$1)) - (B47 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1713,8 +1789,8 @@
         <v>0</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.5923908656261</v>
+        <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.5923908656261</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * COS(RADIANS($F$1)) - (B48 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1733,8 +1809,8 @@
         <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.2884761364538</v>
+        <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.2884761364538</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * COS(RADIANS($F$1)) - (B49 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1753,8 +1829,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.9471392997207</v>
+        <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.9471392997207</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * COS(RADIANS($F$1)) - (B50 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1773,8 +1849,8 @@
         <v>0</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.5688275904869</v>
+        <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.5688275904869</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * COS(RADIANS($F$1)) - (B51 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1793,8 +1869,8 @@
         <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.1543347242093</v>
+        <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.1543347242093</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * COS(RADIANS($F$1)) - (B52 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1813,8 +1889,8 @@
         <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.70495874397016</v>
+        <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.7049587439702</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * COS(RADIANS($F$1)) - (B53 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1833,8 +1909,8 @@
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.22217401164426</v>
+        <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.2221740116443</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * COS(RADIANS($F$1)) - (B54 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1853,8 +1929,8 @@
         <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.70726625593808</v>
+        <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.7072662559381</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * COS(RADIANS($F$1)) - (B55 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1873,8 +1949,8 @@
         <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.16220185197588</v>
+        <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.1622018519759</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * COS(RADIANS($F$1)) - (B56 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1893,8 +1969,8 @@
         <v>0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.58894717488194</v>
+        <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.5889471748819</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * COS(RADIANS($F$1)) - (B57 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1913,8 +1989,8 @@
         <v>0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.9894501282168</v>
+        <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.9894501282168</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * COS(RADIANS($F$1)) - (B58 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1933,8 +2009,8 @@
         <v>0</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.365992781562</v>
+        <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.365992781562</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * COS(RADIANS($F$1)) - (B59 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1953,8 +2029,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.72066857133091</v>
+        <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.7206685713309</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * COS(RADIANS($F$1)) - (B60 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1973,8 +2049,8 @@
         <v>0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.0555524623732</v>
+        <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.0555524623732</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * COS(RADIANS($F$1)) - (B61 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -1993,8 +2069,8 @@
         <v>0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.37271326235061</v>
+        <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.3727132623506</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * COS(RADIANS($F$1)) - (B62 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2013,8 +2089,8 @@
         <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.67401883138096</v>
+        <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.674018831381</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * COS(RADIANS($F$1)) - (B63 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2033,8 +2109,8 @@
         <v>0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.96150103399856</v>
+        <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.9615010339986</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * COS(RADIANS($F$1)) - (B64 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2053,8 +2129,8 @@
         <v>0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.23646798800468</v>
+        <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.2364679880047</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * COS(RADIANS($F$1)) - (B65 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2073,8 +2149,8 @@
         <v>0</v>
       </c>
       <c r="D66" s="5" t="n">
-        <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.50056197722152</v>
+        <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.5005619772215</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * COS(RADIANS($F$1)) - (B66 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2093,8 +2169,8 @@
         <v>0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.754713853114039</v>
+        <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.754713853114</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * COS(RADIANS($F$1)) - (B67 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2113,8 +2189,8 @@
         <v>0</v>
       </c>
       <c r="D68" s="5" t="n">
-        <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0</v>
+        <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * COS(RADIANS($F$1)) - (B68 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2133,8 +2209,8 @@
         <v>0</v>
       </c>
       <c r="D69" s="5" t="n">
-        <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.747522257641646</v>
+        <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.2524777423584</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * COS(RADIANS($F$1)) - (B69 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2153,8 +2229,8 @@
         <v>0</v>
       </c>
       <c r="D70" s="5" t="n">
-        <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.47182022408357</v>
+        <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.5281797759164</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * COS(RADIANS($F$1)) - (B70 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2173,8 +2249,8 @@
         <v>0</v>
       </c>
       <c r="D71" s="5" t="n">
-        <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.17185445813542</v>
+        <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.8281455418646</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * COS(RADIANS($F$1)) - (B71 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2193,8 +2269,8 @@
         <v>0</v>
       </c>
       <c r="D72" s="5" t="n">
-        <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.84679262333874</v>
+        <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.1532073766613</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * COS(RADIANS($F$1)) - (B72 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2213,8 +2289,8 @@
         <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.49510326525357</v>
+        <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.5048967347464</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * COS(RADIANS($F$1)) - (B73 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2233,8 +2309,8 @@
         <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.11562603858838</v>
+        <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.8843739614116</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * COS(RADIANS($F$1)) - (B74 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2253,8 +2329,8 @@
         <v>0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.70651379444597</v>
+        <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.293486205554</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * COS(RADIANS($F$1)) - (B75 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2273,8 +2349,8 @@
         <v>0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.26610801709729</v>
+        <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.7338919829027</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * COS(RADIANS($F$1)) - (B76 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2293,8 +2369,8 @@
         <v>0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.79259850077257</v>
+        <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.2074014992274</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * COS(RADIANS($F$1)) - (B77 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2313,8 +2389,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.28418119688995</v>
+        <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.7158188031101</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * COS(RADIANS($F$1)) - (B78 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2333,8 +2409,8 @@
         <v>0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.73907052843127</v>
+        <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.2609294715687</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * COS(RADIANS($F$1)) - (B79 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2353,8 +2429,8 @@
         <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.15531691396184</v>
+        <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.8446830860382</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * COS(RADIANS($F$1)) - (B80 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2373,8 +2449,8 @@
         <v>0</v>
       </c>
       <c r="D81" s="5" t="n">
-        <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.53134188119539</v>
+        <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.4686581188046</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * COS(RADIANS($F$1)) - (B81 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2393,8 +2469,8 @@
         <v>0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <f aca="false">(( -A82 - (-0.25) ) * SIN(RADIANS($F$1)) + (B82 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.86558542940932</v>
+        <f aca="false">(( -A82 - (-0.25) ) * SIN(RADIANS($F$1)) + (B82 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.1344145705907</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">(( -A82 - (-0.25) ) * COS(RADIANS($F$1)) - (B82 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2413,8 +2489,8 @@
         <v>0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <f aca="false">(( -A83 - (-0.25) ) * SIN(RADIANS($F$1)) + (B83 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.15648755788106</v>
+        <f aca="false">(( -A83 - (-0.25) ) * SIN(RADIANS($F$1)) + (B83 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.8435124421189</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">(( -A83 - (-0.25) ) * COS(RADIANS($F$1)) - (B83 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2433,8 +2509,8 @@
         <v>0</v>
       </c>
       <c r="D84" s="5" t="n">
-        <f aca="false">(( -A84 - (-0.25) ) * SIN(RADIANS($F$1)) + (B84 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.40321816980904</v>
+        <f aca="false">(( -A84 - (-0.25) ) * SIN(RADIANS($F$1)) + (B84 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.596781830191</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">(( -A84 - (-0.25) ) * COS(RADIANS($F$1)) - (B84 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2453,8 +2529,8 @@
         <v>0</v>
       </c>
       <c r="D85" s="5" t="n">
-        <f aca="false">(( -A85 - (-0.25) ) * SIN(RADIANS($F$1)) + (B85 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.60478316397512</v>
+        <f aca="false">(( -A85 - (-0.25) ) * SIN(RADIANS($F$1)) + (B85 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.3952168360249</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">(( -A85 - (-0.25) ) * COS(RADIANS($F$1)) - (B85 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2473,8 +2549,8 @@
         <v>0</v>
       </c>
       <c r="D86" s="5" t="n">
-        <f aca="false">(( -A86 - (-0.25) ) * SIN(RADIANS($F$1)) + (B86 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.76036475795352</v>
+        <f aca="false">(( -A86 - (-0.25) ) * SIN(RADIANS($F$1)) + (B86 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.2396352420465</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">(( -A86 - (-0.25) ) * COS(RADIANS($F$1)) - (B86 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2493,8 +2569,8 @@
         <v>0</v>
       </c>
       <c r="D87" s="5" t="n">
-        <f aca="false">(( -A87 - (-0.25) ) * SIN(RADIANS($F$1)) + (B87 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.86969875444711</v>
+        <f aca="false">(( -A87 - (-0.25) ) * SIN(RADIANS($F$1)) + (B87 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.1303012455529</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">(( -A87 - (-0.25) ) * COS(RADIANS($F$1)) - (B87 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2513,8 +2589,8 @@
         <v>0</v>
       </c>
       <c r="D88" s="5" t="n">
-        <f aca="false">(( -A88 - (-0.25) ) * SIN(RADIANS($F$1)) + (B88 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.93287975093135</v>
+        <f aca="false">(( -A88 - (-0.25) ) * SIN(RADIANS($F$1)) + (B88 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0671202490687</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">(( -A88 - (-0.25) ) * COS(RADIANS($F$1)) - (B88 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2533,8 +2609,8 @@
         <v>0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <f aca="false">(( -A89 - (-0.25) ) * SIN(RADIANS($F$1)) + (B89 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.95001465925749</v>
+        <f aca="false">(( -A89 - (-0.25) ) * SIN(RADIANS($F$1)) + (B89 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0499853407425</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">(( -A89 - (-0.25) ) * COS(RADIANS($F$1)) - (B89 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2553,8 +2629,8 @@
         <v>0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <f aca="false">(( -A90 - (-0.25) ) * SIN(RADIANS($F$1)) + (B90 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.92192182363407</v>
+        <f aca="false">(( -A90 - (-0.25) ) * SIN(RADIANS($F$1)) + (B90 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0780781763659</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">(( -A90 - (-0.25) ) * COS(RADIANS($F$1)) - (B90 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2573,8 +2649,8 @@
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <f aca="false">(( -A91 - (-0.25) ) * SIN(RADIANS($F$1)) + (B91 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.84907310787285</v>
+        <f aca="false">(( -A91 - (-0.25) ) * SIN(RADIANS($F$1)) + (B91 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.1509268921272</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">(( -A91 - (-0.25) ) * COS(RADIANS($F$1)) - (B91 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2593,8 +2669,8 @@
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <f aca="false">(( -A92 - (-0.25) ) * SIN(RADIANS($F$1)) + (B92 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.73301060291543</v>
+        <f aca="false">(( -A92 - (-0.25) ) * SIN(RADIANS($F$1)) + (B92 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.2669893970846</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">(( -A92 - (-0.25) ) * COS(RADIANS($F$1)) - (B92 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2613,8 +2689,8 @@
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <f aca="false">(( -A93 - (-0.25) ) * SIN(RADIANS($F$1)) + (B93 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.57511239528692</v>
+        <f aca="false">(( -A93 - (-0.25) ) * SIN(RADIANS($F$1)) + (B93 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.4248876047131</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">(( -A93 - (-0.25) ) * COS(RADIANS($F$1)) - (B93 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2633,8 +2709,8 @@
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <f aca="false">(( -A94 - (-0.25) ) * SIN(RADIANS($F$1)) + (B94 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.37693289030474</v>
+        <f aca="false">(( -A94 - (-0.25) ) * SIN(RADIANS($F$1)) + (B94 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.6230671096953</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">(( -A94 - (-0.25) ) * COS(RADIANS($F$1)) - (B94 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2653,8 +2729,8 @@
         <v>0</v>
       </c>
       <c r="D95" s="5" t="n">
-        <f aca="false">(( -A95 - (-0.25) ) * SIN(RADIANS($F$1)) + (B95 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.1403914452468</v>
+        <f aca="false">(( -A95 - (-0.25) ) * SIN(RADIANS($F$1)) + (B95 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.8596085547532</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">(( -A95 - (-0.25) ) * COS(RADIANS($F$1)) - (B95 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2673,8 +2749,8 @@
         <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <f aca="false">(( -A96 - (-0.25) ) * SIN(RADIANS($F$1)) + (B96 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.86757142180755</v>
+        <f aca="false">(( -A96 - (-0.25) ) * SIN(RADIANS($F$1)) + (B96 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.1324285781924</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">(( -A96 - (-0.25) ) * COS(RADIANS($F$1)) - (B96 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2693,8 +2769,8 @@
         <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <f aca="false">(( -A97 - (-0.25) ) * SIN(RADIANS($F$1)) + (B97 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.56093344801777</v>
+        <f aca="false">(( -A97 - (-0.25) ) * SIN(RADIANS($F$1)) + (B97 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.4390665519822</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">(( -A97 - (-0.25) ) * COS(RADIANS($F$1)) - (B97 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2713,8 +2789,8 @@
         <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <f aca="false">(( -A98 - (-0.25) ) * SIN(RADIANS($F$1)) + (B98 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.22276183311584</v>
+        <f aca="false">(( -A98 - (-0.25) ) * SIN(RADIANS($F$1)) + (B98 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.7772381668842</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">(( -A98 - (-0.25) ) * COS(RADIANS($F$1)) - (B98 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2733,8 +2809,8 @@
         <v>0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <f aca="false">(( -A99 - (-0.25) ) * SIN(RADIANS($F$1)) + (B99 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.85551104794464</v>
+        <f aca="false">(( -A99 - (-0.25) ) * SIN(RADIANS($F$1)) + (B99 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.1444889520554</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">(( -A99 - (-0.25) ) * COS(RADIANS($F$1)) - (B99 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2753,8 +2829,8 @@
         <v>0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <f aca="false">(( -A100 - (-0.25) ) * SIN(RADIANS($F$1)) + (B100 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.46182419651516</v>
+        <f aca="false">(( -A100 - (-0.25) ) * SIN(RADIANS($F$1)) + (B100 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.5381758034848</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">(( -A100 - (-0.25) ) * COS(RADIANS($F$1)) - (B100 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2773,8 +2849,8 @@
         <v>0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <f aca="false">(( -A101 - (-0.25) ) * SIN(RADIANS($F$1)) + (B101 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.04415574967025</v>
+        <f aca="false">(( -A101 - (-0.25) ) * SIN(RADIANS($F$1)) + (B101 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.9558442503298</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">(( -A101 - (-0.25) ) * COS(RADIANS($F$1)) - (B101 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2793,8 +2869,8 @@
         <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <f aca="false">(( -A102 - (-0.25) ) * SIN(RADIANS($F$1)) + (B102 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.60533128740116</v>
+        <f aca="false">(( -A102 - (-0.25) ) * SIN(RADIANS($F$1)) + (B102 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.3946687125988</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">(( -A102 - (-0.25) ) * COS(RADIANS($F$1)) - (B102 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2813,8 +2889,8 @@
         <v>0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <f aca="false">(( -A103 - (-0.25) ) * SIN(RADIANS($F$1)) + (B103 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.14798159934308</v>
+        <f aca="false">(( -A103 - (-0.25) ) * SIN(RADIANS($F$1)) + (B103 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.8520184006569</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">(( -A103 - (-0.25) ) * COS(RADIANS($F$1)) - (B103 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2833,8 +2909,8 @@
         <v>0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <f aca="false">(( -A104 - (-0.25) ) * SIN(RADIANS($F$1)) + (B104 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.67456731352678</v>
+        <f aca="false">(( -A104 - (-0.25) ) * SIN(RADIANS($F$1)) + (B104 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.3254326864732</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">(( -A104 - (-0.25) ) * COS(RADIANS($F$1)) - (B104 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2853,8 +2929,8 @@
         <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <f aca="false">(( -A105 - (-0.25) ) * SIN(RADIANS($F$1)) + (B105 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.18791400994349</v>
+        <f aca="false">(( -A105 - (-0.25) ) * SIN(RADIANS($F$1)) + (B105 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.8120859900565</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">(( -A105 - (-0.25) ) * COS(RADIANS($F$1)) - (B105 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2873,8 +2949,8 @@
         <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <f aca="false">(( -A106 - (-0.25) ) * SIN(RADIANS($F$1)) + (B106 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.69046384506026</v>
+        <f aca="false">(( -A106 - (-0.25) ) * SIN(RADIANS($F$1)) + (B106 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.3095361549397</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">(( -A106 - (-0.25) ) * COS(RADIANS($F$1)) - (B106 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2893,8 +2969,8 @@
         <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <f aca="false">(( -A107 - (-0.25) ) * SIN(RADIANS($F$1)) + (B107 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.18450112811551</v>
+        <f aca="false">(( -A107 - (-0.25) ) * SIN(RADIANS($F$1)) + (B107 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.8154988718845</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">(( -A107 - (-0.25) ) * COS(RADIANS($F$1)) - (B107 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2913,8 +2989,8 @@
         <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <f aca="false">(( -A108 - (-0.25) ) * SIN(RADIANS($F$1)) + (B108 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.67282681034886</v>
+        <f aca="false">(( -A108 - (-0.25) ) * SIN(RADIANS($F$1)) + (B108 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.3271731896511</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">(( -A108 - (-0.25) ) * COS(RADIANS($F$1)) - (B108 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2933,8 +3009,8 @@
         <v>0</v>
       </c>
       <c r="D109" s="5" t="n">
-        <f aca="false">(( -A109 - (-0.25) ) * SIN(RADIANS($F$1)) + (B109 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.15753656783058</v>
+        <f aca="false">(( -A109 - (-0.25) ) * SIN(RADIANS($F$1)) + (B109 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.8424634321694</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">(( -A109 - (-0.25) ) * COS(RADIANS($F$1)) - (B109 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2953,8 +3029,8 @@
         <v>0</v>
       </c>
       <c r="D110" s="5" t="n">
-        <f aca="false">(( -A110 - (-0.25) ) * SIN(RADIANS($F$1)) + (B110 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.641054085464</v>
+        <f aca="false">(( -A110 - (-0.25) ) * SIN(RADIANS($F$1)) + (B110 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.358945914536</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">(( -A110 - (-0.25) ) * COS(RADIANS($F$1)) - (B110 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2973,8 +3049,8 @@
         <v>0</v>
       </c>
       <c r="D111" s="5" t="n">
-        <f aca="false">(( -A111 - (-0.25) ) * SIN(RADIANS($F$1)) + (B111 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.12546888213147</v>
+        <f aca="false">(( -A111 - (-0.25) ) * SIN(RADIANS($F$1)) + (B111 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.8745311178685</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">(( -A111 - (-0.25) ) * COS(RADIANS($F$1)) - (B111 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -2993,8 +3069,8 @@
         <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <f aca="false">(( -A112 - (-0.25) ) * SIN(RADIANS($F$1)) + (B112 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.613380961528663</v>
+        <f aca="false">(( -A112 - (-0.25) ) * SIN(RADIANS($F$1)) + (B112 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.3866190384713</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">(( -A112 - (-0.25) ) * COS(RADIANS($F$1)) - (B112 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3013,8 +3089,8 @@
         <v>0</v>
       </c>
       <c r="D113" s="5" t="n">
-        <f aca="false">(( -A113 - (-0.25) ) * SIN(RADIANS($F$1)) + (B113 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.106496419013736</v>
+        <f aca="false">(( -A113 - (-0.25) ) * SIN(RADIANS($F$1)) + (B113 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.8935035809863</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">(( -A113 - (-0.25) ) * COS(RADIANS($F$1)) - (B113 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3033,8 +3109,8 @@
         <v>0</v>
       </c>
       <c r="D114" s="5" t="n">
-        <f aca="false">(( -A114 - (-0.25) ) * SIN(RADIANS($F$1)) + (B114 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.392779532073702</v>
+        <f aca="false">(( -A114 - (-0.25) ) * SIN(RADIANS($F$1)) + (B114 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.3927795320737</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">(( -A114 - (-0.25) ) * COS(RADIANS($F$1)) - (B114 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3053,8 +3129,8 @@
         <v>0</v>
       </c>
       <c r="D115" s="5" t="n">
-        <f aca="false">(( -A115 - (-0.25) ) * SIN(RADIANS($F$1)) + (B115 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.88257679195896</v>
+        <f aca="false">(( -A115 - (-0.25) ) * SIN(RADIANS($F$1)) + (B115 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.882576791959</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">(( -A115 - (-0.25) ) * COS(RADIANS($F$1)) - (B115 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3073,8 +3149,8 @@
         <v>0</v>
       </c>
       <c r="D116" s="5" t="n">
-        <f aca="false">(( -A116 - (-0.25) ) * SIN(RADIANS($F$1)) + (B116 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.36050861886614</v>
+        <f aca="false">(( -A116 - (-0.25) ) * SIN(RADIANS($F$1)) + (B116 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.3605086188661</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">(( -A116 - (-0.25) ) * COS(RADIANS($F$1)) - (B116 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3093,8 +3169,8 @@
         <v>0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <f aca="false">(( -A117 - (-0.25) ) * SIN(RADIANS($F$1)) + (B117 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.82490586056452</v>
+        <f aca="false">(( -A117 - (-0.25) ) * SIN(RADIANS($F$1)) + (B117 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.8249058605645</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">(( -A117 - (-0.25) ) * COS(RADIANS($F$1)) - (B117 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3113,8 +3189,8 @@
         <v>0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <f aca="false">(( -A118 - (-0.25) ) * SIN(RADIANS($F$1)) + (B118 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.27357040844634</v>
+        <f aca="false">(( -A118 - (-0.25) ) * SIN(RADIANS($F$1)) + (B118 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.2735704084463</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">(( -A118 - (-0.25) ) * COS(RADIANS($F$1)) - (B118 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3133,8 +3209,8 @@
         <v>0</v>
       </c>
       <c r="D119" s="5" t="n">
-        <f aca="false">(( -A119 - (-0.25) ) * SIN(RADIANS($F$1)) + (B119 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.70451741582363</v>
+        <f aca="false">(( -A119 - (-0.25) ) * SIN(RADIANS($F$1)) + (B119 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.7045174158236</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">(( -A119 - (-0.25) ) * COS(RADIANS($F$1)) - (B119 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3153,8 +3229,8 @@
         <v>0</v>
       </c>
       <c r="D120" s="5" t="n">
-        <f aca="false">(( -A120 - (-0.25) ) * SIN(RADIANS($F$1)) + (B120 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.11593219761284</v>
+        <f aca="false">(( -A120 - (-0.25) ) * SIN(RADIANS($F$1)) + (B120 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.1159321976128</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">(( -A120 - (-0.25) ) * COS(RADIANS($F$1)) - (B120 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3173,8 +3249,8 @@
         <v>0</v>
       </c>
       <c r="D121" s="5" t="n">
-        <f aca="false">(( -A121 - (-0.25) ) * SIN(RADIANS($F$1)) + (B121 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.50582990712598</v>
+        <f aca="false">(( -A121 - (-0.25) ) * SIN(RADIANS($F$1)) + (B121 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.505829907126</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">(( -A121 - (-0.25) ) * COS(RADIANS($F$1)) - (B121 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3193,8 +3269,8 @@
         <v>0</v>
       </c>
       <c r="D122" s="5" t="n">
-        <f aca="false">(( -A122 - (-0.25) ) * SIN(RADIANS($F$1)) + (B122 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.8722626408025</v>
+        <f aca="false">(( -A122 - (-0.25) ) * SIN(RADIANS($F$1)) + (B122 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.8722626408025</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">(( -A122 - (-0.25) ) * COS(RADIANS($F$1)) - (B122 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3213,8 +3289,8 @@
         <v>0</v>
       </c>
       <c r="D123" s="5" t="n">
-        <f aca="false">(( -A123 - (-0.25) ) * SIN(RADIANS($F$1)) + (B123 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.21380529427098</v>
+        <f aca="false">(( -A123 - (-0.25) ) * SIN(RADIANS($F$1)) + (B123 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.213805294271</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">(( -A123 - (-0.25) ) * COS(RADIANS($F$1)) - (B123 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3233,8 +3309,8 @@
         <v>0</v>
       </c>
       <c r="D124" s="5" t="n">
-        <f aca="false">(( -A124 - (-0.25) ) * SIN(RADIANS($F$1)) + (B124 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.52852843553456</v>
+        <f aca="false">(( -A124 - (-0.25) ) * SIN(RADIANS($F$1)) + (B124 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.5285284355346</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">(( -A124 - (-0.25) ) * COS(RADIANS($F$1)) - (B124 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3253,8 +3329,8 @@
         <v>0</v>
       </c>
       <c r="D125" s="5" t="n">
-        <f aca="false">(( -A125 - (-0.25) ) * SIN(RADIANS($F$1)) + (B125 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.81486758455689</v>
+        <f aca="false">(( -A125 - (-0.25) ) * SIN(RADIANS($F$1)) + (B125 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.8148675845569</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">(( -A125 - (-0.25) ) * COS(RADIANS($F$1)) - (B125 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3273,8 +3349,8 @@
         <v>0</v>
       </c>
       <c r="D126" s="5" t="n">
-        <f aca="false">(( -A126 - (-0.25) ) * SIN(RADIANS($F$1)) + (B126 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.07127673286535</v>
+        <f aca="false">(( -A126 - (-0.25) ) * SIN(RADIANS($F$1)) + (B126 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.0712767328654</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">(( -A126 - (-0.25) ) * COS(RADIANS($F$1)) - (B126 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3293,8 +3369,8 @@
         <v>0</v>
       </c>
       <c r="D127" s="5" t="n">
-        <f aca="false">(( -A127 - (-0.25) ) * SIN(RADIANS($F$1)) + (B127 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.29656866675988</v>
+        <f aca="false">(( -A127 - (-0.25) ) * SIN(RADIANS($F$1)) + (B127 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.2965686667599</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">(( -A127 - (-0.25) ) * COS(RADIANS($F$1)) - (B127 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3313,8 +3389,8 @@
         <v>0</v>
       </c>
       <c r="D128" s="5" t="n">
-        <f aca="false">(( -A128 - (-0.25) ) * SIN(RADIANS($F$1)) + (B128 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.48940448249972</v>
+        <f aca="false">(( -A128 - (-0.25) ) * SIN(RADIANS($F$1)) + (B128 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.4894044824997</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">(( -A128 - (-0.25) ) * COS(RADIANS($F$1)) - (B128 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3333,8 +3409,8 @@
         <v>0</v>
       </c>
       <c r="D129" s="5" t="n">
-        <f aca="false">(( -A129 - (-0.25) ) * SIN(RADIANS($F$1)) + (B129 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.64845759071989</v>
+        <f aca="false">(( -A129 - (-0.25) ) * SIN(RADIANS($F$1)) + (B129 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.6484575907199</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">(( -A129 - (-0.25) ) * COS(RADIANS($F$1)) - (B129 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3353,8 +3429,8 @@
         <v>0</v>
       </c>
       <c r="D130" s="5" t="n">
-        <f aca="false">(( -A130 - (-0.25) ) * SIN(RADIANS($F$1)) + (B130 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.77330146758087</v>
+        <f aca="false">(( -A130 - (-0.25) ) * SIN(RADIANS($F$1)) + (B130 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.7733014675809</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">(( -A130 - (-0.25) ) * COS(RADIANS($F$1)) - (B130 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3373,8 +3449,8 @@
         <v>0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <f aca="false">(( -A131 - (-0.25) ) * SIN(RADIANS($F$1)) + (B131 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.86299910442981</v>
+        <f aca="false">(( -A131 - (-0.25) ) * SIN(RADIANS($F$1)) + (B131 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.8629991044298</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">(( -A131 - (-0.25) ) * COS(RADIANS($F$1)) - (B131 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3393,8 +3469,8 @@
         <v>0</v>
       </c>
       <c r="D132" s="5" t="n">
-        <f aca="false">(( -A132 - (-0.25) ) * SIN(RADIANS($F$1)) + (B132 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.91697228738643</v>
+        <f aca="false">(( -A132 - (-0.25) ) * SIN(RADIANS($F$1)) + (B132 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.9169722873864</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">(( -A132 - (-0.25) ) * COS(RADIANS($F$1)) - (B132 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3413,8 +3489,8 @@
         <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <f aca="false">(( -A133 - (-0.25) ) * SIN(RADIANS($F$1)) + (B133 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.15718790444588</v>
+        <f aca="false">(( -A133 - (-0.25) ) * SIN(RADIANS($F$1)) + (B133 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.1571879044459</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">(( -A133 - (-0.25) ) * COS(RADIANS($F$1)) - (B133 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3437,17 +3513,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>176.426266456864</v>
@@ -3467,37 +3543,43 @@
       <c r="J1" s="3" t="n">
         <v>848.131927603976</v>
       </c>
+      <c r="L1" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3512,15 +3594,15 @@
         <v>207.300863086815</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.15718790444588</v>
+        <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.1571879044459</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * COS(RADIANS($F$1)) - (B3 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
         <v>-1024.47758847485</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
+      <c r="N3" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3535,15 +3617,15 @@
         <v>207.300863086815</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.39021192603294</v>
+        <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.3902119260329</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * COS(RADIANS($F$1)) - (B4 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
         <v>-1024.36635535396</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
+      <c r="N4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3558,8 +3640,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.422634951324</v>
+        <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.422634951324</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * COS(RADIANS($F$1)) - (B5 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3578,8 +3660,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.47646081144163</v>
+        <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.4764608114416</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * COS(RADIANS($F$1)) - (B6 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3598,8 +3680,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.55120980751204</v>
+        <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.551209807512</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * COS(RADIANS($F$1)) - (B7 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3618,8 +3700,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.64605576026466</v>
+        <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.6460557602647</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * COS(RADIANS($F$1)) - (B8 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3638,8 +3720,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.76071991836965</v>
+        <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.7607199183696</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * COS(RADIANS($F$1)) - (B9 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3658,8 +3740,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.89406040809918</v>
+        <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.8940604080992</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * COS(RADIANS($F$1)) - (B10 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3678,8 +3760,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.04494767010125</v>
+        <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.0449476701012</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * COS(RADIANS($F$1)) - (B11 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3698,8 +3780,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.21245309256778</v>
+        <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.2124530925678</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * COS(RADIANS($F$1)) - (B12 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3718,8 +3800,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.39530158329393</v>
+        <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.3953015832939</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * COS(RADIANS($F$1)) - (B13 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3738,8 +3820,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.59223652163859</v>
+        <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.5922365216386</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * COS(RADIANS($F$1)) - (B14 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3758,8 +3840,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.80166096375175</v>
+        <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.8016609637517</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * COS(RADIANS($F$1)) - (B15 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3778,8 +3860,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.02253155091204</v>
+        <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.022531550912</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * COS(RADIANS($F$1)) - (B16 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3798,8 +3880,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.25326981083319</v>
+        <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.2532698108332</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * COS(RADIANS($F$1)) - (B17 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3818,8 +3900,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.49233421435632</v>
+        <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.4923342143563</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * COS(RADIANS($F$1)) - (B18 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3838,8 +3920,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.73836570830283</v>
+        <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.7383657083028</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * COS(RADIANS($F$1)) - (B19 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3858,8 +3940,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.98982276351385</v>
+        <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.9898227635139</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * COS(RADIANS($F$1)) - (B20 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3878,8 +3960,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.24502447516561</v>
+        <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.2450244751656</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * COS(RADIANS($F$1)) - (B21 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3898,8 +3980,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D22" s="5" t="n">
-        <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.50281889481135</v>
+        <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.5028188948114</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * COS(RADIANS($F$1)) - (B22 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3918,8 +4000,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D23" s="5" t="n">
-        <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.76136111321076</v>
+        <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.7613611132108</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * COS(RADIANS($F$1)) - (B23 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3938,8 +4020,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D24" s="5" t="n">
-        <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.0193474918764</v>
+        <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.0193474918764</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * COS(RADIANS($F$1)) - (B24 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3958,8 +4040,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D25" s="5" t="n">
-        <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.2749515931316</v>
+        <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.2749515931316</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * COS(RADIANS($F$1)) - (B25 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3978,8 +4060,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.5270584116571</v>
+        <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.5270584116571</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * COS(RADIANS($F$1)) - (B26 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -3998,8 +4080,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.7736836625476</v>
+        <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.7736836625476</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * COS(RADIANS($F$1)) - (B27 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4018,8 +4100,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D28" s="5" t="n">
-        <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.0133904888387</v>
+        <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.0133904888387</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * COS(RADIANS($F$1)) - (B28 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4038,8 +4120,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D29" s="5" t="n">
-        <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.2443709244174</v>
+        <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.2443709244174</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * COS(RADIANS($F$1)) - (B29 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4058,8 +4140,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D30" s="5" t="n">
-        <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.4651942695073</v>
+        <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.4651942695073</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * COS(RADIANS($F$1)) - (B30 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4078,8 +4160,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D31" s="5" t="n">
-        <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.6737245491623</v>
+        <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.6737245491623</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * COS(RADIANS($F$1)) - (B31 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4098,8 +4180,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D32" s="5" t="n">
-        <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.8683670591894</v>
+        <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.8683670591894</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * COS(RADIANS($F$1)) - (B32 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4118,8 +4200,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D33" s="5" t="n">
-        <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.0473323050392</v>
+        <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.0473323050393</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * COS(RADIANS($F$1)) - (B33 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4138,8 +4220,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D34" s="5" t="n">
-        <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.2085089405177</v>
+        <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.2085089405177</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * COS(RADIANS($F$1)) - (B34 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4158,8 +4240,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.3501259426392</v>
+        <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.3501259426392</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * COS(RADIANS($F$1)) - (B35 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4178,8 +4260,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.470229812438</v>
+        <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.470229812438</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * COS(RADIANS($F$1)) - (B36 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4198,8 +4280,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.5667092037199</v>
+        <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.5667092037199</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * COS(RADIANS($F$1)) - (B37 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4218,8 +4300,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6377869363114</v>
+        <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6377869363114</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * COS(RADIANS($F$1)) - (B38 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4238,8 +4320,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D39" s="5" t="n">
-        <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6815218256228</v>
+        <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6815218256228</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * COS(RADIANS($F$1)) - (B39 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4258,8 +4340,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D40" s="5" t="n">
-        <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6961366914805</v>
+        <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6961366914805</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * COS(RADIANS($F$1)) - (B40 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4278,8 +4360,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D41" s="5" t="n">
-        <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6800368296915</v>
+        <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6800368296915</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * COS(RADIANS($F$1)) - (B41 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4298,8 +4380,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.6314512172704</v>
+        <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.6314512172704</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4318,8 +4400,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.5489368400647</v>
+        <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.5489368400647</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * COS(RADIANS($F$1)) - (B43 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4338,8 +4420,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.4312393170902</v>
+        <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.4312393170902</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * COS(RADIANS($F$1)) - (B44 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4358,8 +4440,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.2774445905715</v>
+        <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.2774445905716</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * COS(RADIANS($F$1)) - (B45 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4378,8 +4460,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.0868149215257</v>
+        <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>37.0868149215257</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * COS(RADIANS($F$1)) - (B46 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4398,8 +4480,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.8584239378015</v>
+        <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.8584239378015</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * COS(RADIANS($F$1)) - (B47 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4418,8 +4500,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.5923908656261</v>
+        <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.5923908656261</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * COS(RADIANS($F$1)) - (B48 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4438,8 +4520,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.2884761364538</v>
+        <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>36.2884761364538</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * COS(RADIANS($F$1)) - (B49 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4458,8 +4540,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.9471392997207</v>
+        <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.9471392997207</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * COS(RADIANS($F$1)) - (B50 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4478,8 +4560,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.5688275904869</v>
+        <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.5688275904869</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * COS(RADIANS($F$1)) - (B51 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4498,8 +4580,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>10.1543347242093</v>
+        <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>35.1543347242093</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * COS(RADIANS($F$1)) - (B52 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4518,8 +4600,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.70495874397016</v>
+        <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.7049587439702</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * COS(RADIANS($F$1)) - (B53 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4538,8 +4620,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>9.22217401164426</v>
+        <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>34.2221740116443</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * COS(RADIANS($F$1)) - (B54 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4558,8 +4640,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.70726625593808</v>
+        <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.7072662559381</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * COS(RADIANS($F$1)) - (B55 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4578,8 +4660,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D56" s="5" t="n">
-        <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.16220185197588</v>
+        <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>33.1622018519759</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * COS(RADIANS($F$1)) - (B56 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4598,8 +4680,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D57" s="5" t="n">
-        <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.58894717488194</v>
+        <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>32.5889471748819</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * COS(RADIANS($F$1)) - (B57 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4618,8 +4700,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D58" s="5" t="n">
-        <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.9894501282168</v>
+        <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.9894501282168</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * COS(RADIANS($F$1)) - (B58 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4638,8 +4720,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.365992781562</v>
+        <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.365992781562</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * COS(RADIANS($F$1)) - (B59 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4658,8 +4740,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.72066857133091</v>
+        <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.7206685713309</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * COS(RADIANS($F$1)) - (B60 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4678,8 +4760,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.0555524623732</v>
+        <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.0555524623732</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * COS(RADIANS($F$1)) - (B61 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4698,8 +4780,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.37271326235061</v>
+        <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.3727132623506</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * COS(RADIANS($F$1)) - (B62 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4718,8 +4800,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D63" s="5" t="n">
-        <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.67401883138096</v>
+        <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.674018831381</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * COS(RADIANS($F$1)) - (B63 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4738,8 +4820,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D64" s="5" t="n">
-        <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.96150103399856</v>
+        <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.9615010339986</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * COS(RADIANS($F$1)) - (B64 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4758,8 +4840,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D65" s="5" t="n">
-        <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.23646798800468</v>
+        <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.2364679880047</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * COS(RADIANS($F$1)) - (B65 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4778,8 +4860,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D66" s="5" t="n">
-        <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.50056197722152</v>
+        <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.5005619772215</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * COS(RADIANS($F$1)) - (B66 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4798,8 +4880,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D67" s="5" t="n">
-        <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.754713853114039</v>
+        <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.754713853114</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * COS(RADIANS($F$1)) - (B67 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4818,8 +4900,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D68" s="5" t="n">
-        <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0</v>
+        <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * COS(RADIANS($F$1)) - (B68 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4838,8 +4920,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D69" s="5" t="n">
-        <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.747522257641646</v>
+        <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.2524777423584</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * COS(RADIANS($F$1)) - (B69 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4858,8 +4940,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D70" s="5" t="n">
-        <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.47182022408357</v>
+        <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.5281797759164</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * COS(RADIANS($F$1)) - (B70 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4878,8 +4960,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D71" s="5" t="n">
-        <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.17185445813542</v>
+        <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.8281455418646</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * COS(RADIANS($F$1)) - (B71 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4898,8 +4980,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D72" s="5" t="n">
-        <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.84679262333874</v>
+        <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.1532073766613</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * COS(RADIANS($F$1)) - (B72 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4918,8 +5000,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D73" s="5" t="n">
-        <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.49510326525357</v>
+        <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.5048967347464</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * COS(RADIANS($F$1)) - (B73 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4938,8 +5020,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D74" s="5" t="n">
-        <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.11562603858838</v>
+        <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.8843739614116</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * COS(RADIANS($F$1)) - (B74 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4958,8 +5040,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D75" s="5" t="n">
-        <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.70651379444597</v>
+        <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.293486205554</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * COS(RADIANS($F$1)) - (B75 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4978,8 +5060,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D76" s="5" t="n">
-        <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.26610801709729</v>
+        <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.7338919829027</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * COS(RADIANS($F$1)) - (B76 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -4998,8 +5080,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D77" s="5" t="n">
-        <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.79259850077257</v>
+        <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.2074014992274</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * COS(RADIANS($F$1)) - (B77 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5018,8 +5100,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D78" s="5" t="n">
-        <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.28418119688995</v>
+        <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.7158188031101</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * COS(RADIANS($F$1)) - (B78 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5038,8 +5120,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D79" s="5" t="n">
-        <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.73907052843127</v>
+        <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.2609294715687</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * COS(RADIANS($F$1)) - (B79 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5058,8 +5140,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D80" s="5" t="n">
-        <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.15531691396184</v>
+        <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.8446830860382</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * COS(RADIANS($F$1)) - (B80 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5078,8 +5160,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D81" s="5" t="n">
-        <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.53134188119539</v>
+        <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.4686581188046</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * COS(RADIANS($F$1)) - (B81 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5098,8 +5180,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D82" s="5" t="n">
-        <f aca="false">(( -A82 - (-0.25) ) * SIN(RADIANS($F$1)) + (B82 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.86558542940932</v>
+        <f aca="false">(( -A82 - (-0.25) ) * SIN(RADIANS($F$1)) + (B82 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.1344145705907</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">(( -A82 - (-0.25) ) * COS(RADIANS($F$1)) - (B82 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5118,8 +5200,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D83" s="5" t="n">
-        <f aca="false">(( -A83 - (-0.25) ) * SIN(RADIANS($F$1)) + (B83 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.15648755788106</v>
+        <f aca="false">(( -A83 - (-0.25) ) * SIN(RADIANS($F$1)) + (B83 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.8435124421189</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">(( -A83 - (-0.25) ) * COS(RADIANS($F$1)) - (B83 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5138,8 +5220,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D84" s="5" t="n">
-        <f aca="false">(( -A84 - (-0.25) ) * SIN(RADIANS($F$1)) + (B84 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.40321816980904</v>
+        <f aca="false">(( -A84 - (-0.25) ) * SIN(RADIANS($F$1)) + (B84 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.596781830191</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">(( -A84 - (-0.25) ) * COS(RADIANS($F$1)) - (B84 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5158,8 +5240,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D85" s="5" t="n">
-        <f aca="false">(( -A85 - (-0.25) ) * SIN(RADIANS($F$1)) + (B85 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.60478316397512</v>
+        <f aca="false">(( -A85 - (-0.25) ) * SIN(RADIANS($F$1)) + (B85 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.3952168360249</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">(( -A85 - (-0.25) ) * COS(RADIANS($F$1)) - (B85 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5178,8 +5260,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D86" s="5" t="n">
-        <f aca="false">(( -A86 - (-0.25) ) * SIN(RADIANS($F$1)) + (B86 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.76036475795352</v>
+        <f aca="false">(( -A86 - (-0.25) ) * SIN(RADIANS($F$1)) + (B86 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.2396352420465</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">(( -A86 - (-0.25) ) * COS(RADIANS($F$1)) - (B86 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5198,8 +5280,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D87" s="5" t="n">
-        <f aca="false">(( -A87 - (-0.25) ) * SIN(RADIANS($F$1)) + (B87 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.86969875444711</v>
+        <f aca="false">(( -A87 - (-0.25) ) * SIN(RADIANS($F$1)) + (B87 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.1303012455529</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">(( -A87 - (-0.25) ) * COS(RADIANS($F$1)) - (B87 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5218,8 +5300,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D88" s="5" t="n">
-        <f aca="false">(( -A88 - (-0.25) ) * SIN(RADIANS($F$1)) + (B88 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.93287975093135</v>
+        <f aca="false">(( -A88 - (-0.25) ) * SIN(RADIANS($F$1)) + (B88 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0671202490687</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">(( -A88 - (-0.25) ) * COS(RADIANS($F$1)) - (B88 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5238,8 +5320,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D89" s="5" t="n">
-        <f aca="false">(( -A89 - (-0.25) ) * SIN(RADIANS($F$1)) + (B89 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.95001465925749</v>
+        <f aca="false">(( -A89 - (-0.25) ) * SIN(RADIANS($F$1)) + (B89 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0499853407425</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">(( -A89 - (-0.25) ) * COS(RADIANS($F$1)) - (B89 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5258,8 +5340,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D90" s="5" t="n">
-        <f aca="false">(( -A90 - (-0.25) ) * SIN(RADIANS($F$1)) + (B90 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.92192182363407</v>
+        <f aca="false">(( -A90 - (-0.25) ) * SIN(RADIANS($F$1)) + (B90 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.0780781763659</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">(( -A90 - (-0.25) ) * COS(RADIANS($F$1)) - (B90 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5278,8 +5360,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D91" s="5" t="n">
-        <f aca="false">(( -A91 - (-0.25) ) * SIN(RADIANS($F$1)) + (B91 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.84907310787285</v>
+        <f aca="false">(( -A91 - (-0.25) ) * SIN(RADIANS($F$1)) + (B91 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.1509268921272</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">(( -A91 - (-0.25) ) * COS(RADIANS($F$1)) - (B91 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5298,8 +5380,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D92" s="5" t="n">
-        <f aca="false">(( -A92 - (-0.25) ) * SIN(RADIANS($F$1)) + (B92 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.73301060291543</v>
+        <f aca="false">(( -A92 - (-0.25) ) * SIN(RADIANS($F$1)) + (B92 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.2669893970846</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">(( -A92 - (-0.25) ) * COS(RADIANS($F$1)) - (B92 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5318,8 +5400,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D93" s="5" t="n">
-        <f aca="false">(( -A93 - (-0.25) ) * SIN(RADIANS($F$1)) + (B93 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.57511239528692</v>
+        <f aca="false">(( -A93 - (-0.25) ) * SIN(RADIANS($F$1)) + (B93 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.4248876047131</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">(( -A93 - (-0.25) ) * COS(RADIANS($F$1)) - (B93 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5338,8 +5420,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D94" s="5" t="n">
-        <f aca="false">(( -A94 - (-0.25) ) * SIN(RADIANS($F$1)) + (B94 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.37693289030474</v>
+        <f aca="false">(( -A94 - (-0.25) ) * SIN(RADIANS($F$1)) + (B94 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.6230671096953</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">(( -A94 - (-0.25) ) * COS(RADIANS($F$1)) - (B94 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5358,8 +5440,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D95" s="5" t="n">
-        <f aca="false">(( -A95 - (-0.25) ) * SIN(RADIANS($F$1)) + (B95 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.1403914452468</v>
+        <f aca="false">(( -A95 - (-0.25) ) * SIN(RADIANS($F$1)) + (B95 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>16.8596085547532</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">(( -A95 - (-0.25) ) * COS(RADIANS($F$1)) - (B95 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5378,8 +5460,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D96" s="5" t="n">
-        <f aca="false">(( -A96 - (-0.25) ) * SIN(RADIANS($F$1)) + (B96 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.86757142180755</v>
+        <f aca="false">(( -A96 - (-0.25) ) * SIN(RADIANS($F$1)) + (B96 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.1324285781924</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">(( -A96 - (-0.25) ) * COS(RADIANS($F$1)) - (B96 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5398,8 +5480,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D97" s="5" t="n">
-        <f aca="false">(( -A97 - (-0.25) ) * SIN(RADIANS($F$1)) + (B97 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.56093344801777</v>
+        <f aca="false">(( -A97 - (-0.25) ) * SIN(RADIANS($F$1)) + (B97 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.4390665519822</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">(( -A97 - (-0.25) ) * COS(RADIANS($F$1)) - (B97 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5418,8 +5500,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D98" s="5" t="n">
-        <f aca="false">(( -A98 - (-0.25) ) * SIN(RADIANS($F$1)) + (B98 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.22276183311584</v>
+        <f aca="false">(( -A98 - (-0.25) ) * SIN(RADIANS($F$1)) + (B98 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>17.7772381668842</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">(( -A98 - (-0.25) ) * COS(RADIANS($F$1)) - (B98 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5438,8 +5520,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D99" s="5" t="n">
-        <f aca="false">(( -A99 - (-0.25) ) * SIN(RADIANS($F$1)) + (B99 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.85551104794464</v>
+        <f aca="false">(( -A99 - (-0.25) ) * SIN(RADIANS($F$1)) + (B99 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.1444889520554</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">(( -A99 - (-0.25) ) * COS(RADIANS($F$1)) - (B99 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5458,8 +5540,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D100" s="5" t="n">
-        <f aca="false">(( -A100 - (-0.25) ) * SIN(RADIANS($F$1)) + (B100 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.46182419651516</v>
+        <f aca="false">(( -A100 - (-0.25) ) * SIN(RADIANS($F$1)) + (B100 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.5381758034848</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">(( -A100 - (-0.25) ) * COS(RADIANS($F$1)) - (B100 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5478,8 +5560,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D101" s="5" t="n">
-        <f aca="false">(( -A101 - (-0.25) ) * SIN(RADIANS($F$1)) + (B101 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.04415574967025</v>
+        <f aca="false">(( -A101 - (-0.25) ) * SIN(RADIANS($F$1)) + (B101 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>18.9558442503298</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">(( -A101 - (-0.25) ) * COS(RADIANS($F$1)) - (B101 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5498,8 +5580,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D102" s="5" t="n">
-        <f aca="false">(( -A102 - (-0.25) ) * SIN(RADIANS($F$1)) + (B102 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.60533128740116</v>
+        <f aca="false">(( -A102 - (-0.25) ) * SIN(RADIANS($F$1)) + (B102 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.3946687125988</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">(( -A102 - (-0.25) ) * COS(RADIANS($F$1)) - (B102 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5518,8 +5600,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D103" s="5" t="n">
-        <f aca="false">(( -A103 - (-0.25) ) * SIN(RADIANS($F$1)) + (B103 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-5.14798159934308</v>
+        <f aca="false">(( -A103 - (-0.25) ) * SIN(RADIANS($F$1)) + (B103 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>19.8520184006569</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">(( -A103 - (-0.25) ) * COS(RADIANS($F$1)) - (B103 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5538,8 +5620,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D104" s="5" t="n">
-        <f aca="false">(( -A104 - (-0.25) ) * SIN(RADIANS($F$1)) + (B104 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.67456731352678</v>
+        <f aca="false">(( -A104 - (-0.25) ) * SIN(RADIANS($F$1)) + (B104 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.3254326864732</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">(( -A104 - (-0.25) ) * COS(RADIANS($F$1)) - (B104 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5558,8 +5640,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D105" s="5" t="n">
-        <f aca="false">(( -A105 - (-0.25) ) * SIN(RADIANS($F$1)) + (B105 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.18791400994349</v>
+        <f aca="false">(( -A105 - (-0.25) ) * SIN(RADIANS($F$1)) + (B105 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>20.8120859900565</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">(( -A105 - (-0.25) ) * COS(RADIANS($F$1)) - (B105 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5578,8 +5660,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D106" s="5" t="n">
-        <f aca="false">(( -A106 - (-0.25) ) * SIN(RADIANS($F$1)) + (B106 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.69046384506026</v>
+        <f aca="false">(( -A106 - (-0.25) ) * SIN(RADIANS($F$1)) + (B106 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.3095361549397</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">(( -A106 - (-0.25) ) * COS(RADIANS($F$1)) - (B106 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5598,8 +5680,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D107" s="5" t="n">
-        <f aca="false">(( -A107 - (-0.25) ) * SIN(RADIANS($F$1)) + (B107 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-3.18450112811551</v>
+        <f aca="false">(( -A107 - (-0.25) ) * SIN(RADIANS($F$1)) + (B107 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>21.8154988718845</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">(( -A107 - (-0.25) ) * COS(RADIANS($F$1)) - (B107 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5618,8 +5700,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D108" s="5" t="n">
-        <f aca="false">(( -A108 - (-0.25) ) * SIN(RADIANS($F$1)) + (B108 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.67282681034886</v>
+        <f aca="false">(( -A108 - (-0.25) ) * SIN(RADIANS($F$1)) + (B108 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.3271731896511</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">(( -A108 - (-0.25) ) * COS(RADIANS($F$1)) - (B108 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5638,8 +5720,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D109" s="5" t="n">
-        <f aca="false">(( -A109 - (-0.25) ) * SIN(RADIANS($F$1)) + (B109 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.15753656783058</v>
+        <f aca="false">(( -A109 - (-0.25) ) * SIN(RADIANS($F$1)) + (B109 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>22.8424634321694</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">(( -A109 - (-0.25) ) * COS(RADIANS($F$1)) - (B109 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5658,8 +5740,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D110" s="5" t="n">
-        <f aca="false">(( -A110 - (-0.25) ) * SIN(RADIANS($F$1)) + (B110 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.641054085464</v>
+        <f aca="false">(( -A110 - (-0.25) ) * SIN(RADIANS($F$1)) + (B110 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.358945914536</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">(( -A110 - (-0.25) ) * COS(RADIANS($F$1)) - (B110 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5678,8 +5760,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D111" s="5" t="n">
-        <f aca="false">(( -A111 - (-0.25) ) * SIN(RADIANS($F$1)) + (B111 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.12546888213147</v>
+        <f aca="false">(( -A111 - (-0.25) ) * SIN(RADIANS($F$1)) + (B111 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>23.8745311178685</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">(( -A111 - (-0.25) ) * COS(RADIANS($F$1)) - (B111 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5698,8 +5780,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D112" s="5" t="n">
-        <f aca="false">(( -A112 - (-0.25) ) * SIN(RADIANS($F$1)) + (B112 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.613380961528663</v>
+        <f aca="false">(( -A112 - (-0.25) ) * SIN(RADIANS($F$1)) + (B112 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.3866190384713</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">(( -A112 - (-0.25) ) * COS(RADIANS($F$1)) - (B112 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5718,8 +5800,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D113" s="5" t="n">
-        <f aca="false">(( -A113 - (-0.25) ) * SIN(RADIANS($F$1)) + (B113 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.106496419013736</v>
+        <f aca="false">(( -A113 - (-0.25) ) * SIN(RADIANS($F$1)) + (B113 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>24.8935035809863</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">(( -A113 - (-0.25) ) * COS(RADIANS($F$1)) - (B113 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5738,8 +5820,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D114" s="5" t="n">
-        <f aca="false">(( -A114 - (-0.25) ) * SIN(RADIANS($F$1)) + (B114 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.392779532073702</v>
+        <f aca="false">(( -A114 - (-0.25) ) * SIN(RADIANS($F$1)) + (B114 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.3927795320737</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">(( -A114 - (-0.25) ) * COS(RADIANS($F$1)) - (B114 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5758,8 +5840,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D115" s="5" t="n">
-        <f aca="false">(( -A115 - (-0.25) ) * SIN(RADIANS($F$1)) + (B115 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.88257679195896</v>
+        <f aca="false">(( -A115 - (-0.25) ) * SIN(RADIANS($F$1)) + (B115 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>25.882576791959</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">(( -A115 - (-0.25) ) * COS(RADIANS($F$1)) - (B115 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5778,8 +5860,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D116" s="5" t="n">
-        <f aca="false">(( -A116 - (-0.25) ) * SIN(RADIANS($F$1)) + (B116 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.36050861886614</v>
+        <f aca="false">(( -A116 - (-0.25) ) * SIN(RADIANS($F$1)) + (B116 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.3605086188661</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">(( -A116 - (-0.25) ) * COS(RADIANS($F$1)) - (B116 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5798,8 +5880,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D117" s="5" t="n">
-        <f aca="false">(( -A117 - (-0.25) ) * SIN(RADIANS($F$1)) + (B117 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.82490586056452</v>
+        <f aca="false">(( -A117 - (-0.25) ) * SIN(RADIANS($F$1)) + (B117 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>26.8249058605645</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">(( -A117 - (-0.25) ) * COS(RADIANS($F$1)) - (B117 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5818,8 +5900,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D118" s="5" t="n">
-        <f aca="false">(( -A118 - (-0.25) ) * SIN(RADIANS($F$1)) + (B118 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.27357040844634</v>
+        <f aca="false">(( -A118 - (-0.25) ) * SIN(RADIANS($F$1)) + (B118 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.2735704084463</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">(( -A118 - (-0.25) ) * COS(RADIANS($F$1)) - (B118 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5838,8 +5920,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D119" s="5" t="n">
-        <f aca="false">(( -A119 - (-0.25) ) * SIN(RADIANS($F$1)) + (B119 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.70451741582363</v>
+        <f aca="false">(( -A119 - (-0.25) ) * SIN(RADIANS($F$1)) + (B119 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>27.7045174158236</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">(( -A119 - (-0.25) ) * COS(RADIANS($F$1)) - (B119 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5858,8 +5940,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D120" s="5" t="n">
-        <f aca="false">(( -A120 - (-0.25) ) * SIN(RADIANS($F$1)) + (B120 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.11593219761284</v>
+        <f aca="false">(( -A120 - (-0.25) ) * SIN(RADIANS($F$1)) + (B120 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.1159321976128</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">(( -A120 - (-0.25) ) * COS(RADIANS($F$1)) - (B120 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5878,8 +5960,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D121" s="5" t="n">
-        <f aca="false">(( -A121 - (-0.25) ) * SIN(RADIANS($F$1)) + (B121 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.50582990712598</v>
+        <f aca="false">(( -A121 - (-0.25) ) * SIN(RADIANS($F$1)) + (B121 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.505829907126</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">(( -A121 - (-0.25) ) * COS(RADIANS($F$1)) - (B121 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5898,8 +5980,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D122" s="5" t="n">
-        <f aca="false">(( -A122 - (-0.25) ) * SIN(RADIANS($F$1)) + (B122 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.8722626408025</v>
+        <f aca="false">(( -A122 - (-0.25) ) * SIN(RADIANS($F$1)) + (B122 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>28.8722626408025</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">(( -A122 - (-0.25) ) * COS(RADIANS($F$1)) - (B122 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5918,8 +6000,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D123" s="5" t="n">
-        <f aca="false">(( -A123 - (-0.25) ) * SIN(RADIANS($F$1)) + (B123 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.21380529427098</v>
+        <f aca="false">(( -A123 - (-0.25) ) * SIN(RADIANS($F$1)) + (B123 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.213805294271</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">(( -A123 - (-0.25) ) * COS(RADIANS($F$1)) - (B123 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5938,8 +6020,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D124" s="5" t="n">
-        <f aca="false">(( -A124 - (-0.25) ) * SIN(RADIANS($F$1)) + (B124 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.52852843553456</v>
+        <f aca="false">(( -A124 - (-0.25) ) * SIN(RADIANS($F$1)) + (B124 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.5285284355346</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">(( -A124 - (-0.25) ) * COS(RADIANS($F$1)) - (B124 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5958,8 +6040,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D125" s="5" t="n">
-        <f aca="false">(( -A125 - (-0.25) ) * SIN(RADIANS($F$1)) + (B125 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.81486758455689</v>
+        <f aca="false">(( -A125 - (-0.25) ) * SIN(RADIANS($F$1)) + (B125 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>29.8148675845569</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">(( -A125 - (-0.25) ) * COS(RADIANS($F$1)) - (B125 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5978,8 +6060,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D126" s="5" t="n">
-        <f aca="false">(( -A126 - (-0.25) ) * SIN(RADIANS($F$1)) + (B126 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.07127673286535</v>
+        <f aca="false">(( -A126 - (-0.25) ) * SIN(RADIANS($F$1)) + (B126 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.0712767328654</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">(( -A126 - (-0.25) ) * COS(RADIANS($F$1)) - (B126 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -5998,8 +6080,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D127" s="5" t="n">
-        <f aca="false">(( -A127 - (-0.25) ) * SIN(RADIANS($F$1)) + (B127 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.29656866675988</v>
+        <f aca="false">(( -A127 - (-0.25) ) * SIN(RADIANS($F$1)) + (B127 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.2965686667599</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">(( -A127 - (-0.25) ) * COS(RADIANS($F$1)) - (B127 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6018,8 +6100,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D128" s="5" t="n">
-        <f aca="false">(( -A128 - (-0.25) ) * SIN(RADIANS($F$1)) + (B128 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.48940448249972</v>
+        <f aca="false">(( -A128 - (-0.25) ) * SIN(RADIANS($F$1)) + (B128 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.4894044824997</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">(( -A128 - (-0.25) ) * COS(RADIANS($F$1)) - (B128 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6038,8 +6120,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D129" s="5" t="n">
-        <f aca="false">(( -A129 - (-0.25) ) * SIN(RADIANS($F$1)) + (B129 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.64845759071989</v>
+        <f aca="false">(( -A129 - (-0.25) ) * SIN(RADIANS($F$1)) + (B129 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.6484575907199</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">(( -A129 - (-0.25) ) * COS(RADIANS($F$1)) - (B129 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6058,8 +6140,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D130" s="5" t="n">
-        <f aca="false">(( -A130 - (-0.25) ) * SIN(RADIANS($F$1)) + (B130 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.77330146758087</v>
+        <f aca="false">(( -A130 - (-0.25) ) * SIN(RADIANS($F$1)) + (B130 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.7733014675809</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">(( -A130 - (-0.25) ) * COS(RADIANS($F$1)) - (B130 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6078,8 +6160,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D131" s="5" t="n">
-        <f aca="false">(( -A131 - (-0.25) ) * SIN(RADIANS($F$1)) + (B131 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.86299910442981</v>
+        <f aca="false">(( -A131 - (-0.25) ) * SIN(RADIANS($F$1)) + (B131 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.8629991044298</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">(( -A131 - (-0.25) ) * COS(RADIANS($F$1)) - (B131 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6098,8 +6180,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D132" s="5" t="n">
-        <f aca="false">(( -A132 - (-0.25) ) * SIN(RADIANS($F$1)) + (B132 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.91697228738643</v>
+        <f aca="false">(( -A132 - (-0.25) ) * SIN(RADIANS($F$1)) + (B132 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>30.9169722873864</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">(( -A132 - (-0.25) ) * COS(RADIANS($F$1)) - (B132 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6118,8 +6200,8 @@
         <v>207.300863086815</v>
       </c>
       <c r="D133" s="5" t="n">
-        <f aca="false">(( -A133 - (-0.25) ) * SIN(RADIANS($F$1)) + (B133 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.15718790444588</v>
+        <f aca="false">(( -A133 - (-0.25) ) * SIN(RADIANS($F$1)) + (B133 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1))) + $L$1</f>
+        <v>31.1571879044459</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">(( -A133 - (-0.25) ) * COS(RADIANS($F$1)) - (B133 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1))) - $J$1</f>
@@ -6142,17 +6224,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>175.784845883201</v>
@@ -6172,37 +6254,43 @@
       <c r="K1" s="3" t="n">
         <v>35.78915</v>
       </c>
+      <c r="L1" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6217,15 +6305,15 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">-A3*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1024.07712863059</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
+      <c r="N3" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6240,15 +6328,15 @@
         <v>0.235903263175255</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">-A4*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1023.9744702806</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
+      <c r="N4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6263,8 +6351,8 @@
         <v>0.278970550416639</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">-A5*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6283,8 +6371,8 @@
         <v>0.350514982691102</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">-A6*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6303,8 +6391,8 @@
         <v>0.450009205460993</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">-A7*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6323,8 +6411,8 @@
         <v>0.576574294496898</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">-A8*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6343,8 +6431,8 @@
         <v>0.729858680107049</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">-A9*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6363,8 +6451,8 @@
         <v>0.908631868370263</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">-A10*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6383,8 +6471,8 @@
         <v>1.11166336536536</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">-A11*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6403,8 +6491,8 @@
         <v>1.33789846201704</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">-A12*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6423,8 +6511,8 @@
         <v>1.58593087955824</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">-A13*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6443,8 +6531,8 @@
         <v>1.85435433922188</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">-A14*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6463,8 +6551,8 @@
         <v>2.14141099254915</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">-A15*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6483,8 +6571,8 @@
         <v>2.44587034561885</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">-A16*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6503,8 +6591,8 @@
         <v>2.76597454997216</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">-A17*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6523,8 +6611,8 @@
         <v>3.09996575715024</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">-A18*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6543,8 +6631,8 @@
         <v>3.44626190354015</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">-A19*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6563,8 +6651,8 @@
         <v>3.80310514068304</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">-A20*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6583,8 +6671,8 @@
         <v>4.16856183527422</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">-A21*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6603,8 +6691,8 @@
         <v>4.5412257085466</v>
       </c>
       <c r="D22" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">-A22*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6623,8 +6711,8 @@
         <v>4.9189873423496</v>
       </c>
       <c r="D23" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">-A23*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6643,8 +6731,8 @@
         <v>5.30026467307026</v>
       </c>
       <c r="D24" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">-A24*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6663,8 +6751,8 @@
         <v>5.68294828255799</v>
       </c>
       <c r="D25" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">-A25*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6683,8 +6771,8 @@
         <v>6.06563189204572</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">-A26*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6703,8 +6791,8 @@
         <v>6.44603029853696</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">-A27*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6723,8 +6811,8 @@
         <v>6.82238565357289</v>
       </c>
       <c r="D28" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">-A28*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6743,8 +6831,8 @@
         <v>7.19258853900292</v>
       </c>
       <c r="D29" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">-A29*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6763,8 +6851,8 @@
         <v>7.55488110636819</v>
       </c>
       <c r="D30" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">-A30*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6783,8 +6871,8 @@
         <v>7.90680236782636</v>
       </c>
       <c r="D31" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">-A31*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6803,8 +6891,8 @@
         <v>8.2464186900727</v>
       </c>
       <c r="D32" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">-A32*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6823,8 +6911,8 @@
         <v>8.57162065495662</v>
       </c>
       <c r="D33" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">-A33*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6843,8 +6931,8 @@
         <v>8.87994727463576</v>
       </c>
       <c r="D34" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">-A34*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6863,8 +6951,8 @@
         <v>9.1692891309595</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">-A35*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6883,8 +6971,8 @@
         <v>9.43736102093138</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">-A36*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6903,8 +6991,8 @@
         <v>9.68170195670903</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">-A37*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6923,8 +7011,8 @@
         <v>9.90020252014185</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">-A38*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6943,8 +7031,8 @@
         <v>10.0905775082334</v>
       </c>
       <c r="D39" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">-A39*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6963,8 +7051,8 @@
         <v>10.250717502833</v>
       </c>
       <c r="D40" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">-A40*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6983,8 +7071,8 @@
         <v>10.3786888706359</v>
       </c>
       <c r="D41" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">-A41*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7003,8 +7091,8 @@
         <v>10.4723821934917</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">-A42*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7023,8 +7111,8 @@
         <v>10.5300396229414</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">-A43*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7043,8 +7131,8 @@
         <v>10.550079095372</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">-A44*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7063,8 +7151,8 @@
         <v>10.5312701168625</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">-A45*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7083,8 +7171,8 @@
         <v>10.4725579783376</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">-A46*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7103,8 +7191,8 @@
         <v>10.3727121858759</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">-A47*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7123,8 +7211,8 @@
         <v>10.2315569546317</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">-A48*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7143,8 +7231,8 @@
         <v>10.0485649300673</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">-A49*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7163,8 +7251,8 @@
         <v>9.82391189702854</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">-A50*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7183,8 +7271,8 @@
         <v>9.55777364036138</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">-A51*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7203,8 +7291,8 @@
         <v>9.25067751460343</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">-A52*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7223,8 +7311,8 @@
         <v>8.90367822882999</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">-A53*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7243,8 +7331,8 @@
         <v>8.51800627696225</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">-A54*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7263,8 +7351,8 @@
         <v>8.0947163680755</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">-A55*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7283,8 +7371,8 @@
         <v>7.63556635062858</v>
       </c>
       <c r="D56" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">-A56*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7303,8 +7391,8 @@
         <v>7.14231407308032</v>
       </c>
       <c r="D57" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">-A57*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7323,8 +7411,8 @@
         <v>6.61671738388955</v>
       </c>
       <c r="D58" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">-A58*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7343,8 +7431,8 @@
         <v>6.06088570120687</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">-A59*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7363,8 +7451,8 @@
         <v>5.47675265833699</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">-A60*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7383,8 +7471,8 @@
         <v>4.86625188858464</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">-A61*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7403,8 +7491,8 @@
         <v>4.23131702525452</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">-A62*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7423,8 +7511,8 @@
         <v>3.57370591680547</v>
       </c>
       <c r="D63" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">-A63*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7443,8 +7531,8 @@
         <v>2.8953521965422</v>
       </c>
       <c r="D64" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">-A64*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7463,8 +7551,8 @@
         <v>2.19748635838589</v>
       </c>
       <c r="D65" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">-A65*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7483,8 +7571,8 @@
         <v>1.4816904659495</v>
       </c>
       <c r="D66" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">-A66*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7503,8 +7591,8 @@
         <v>0.748843443462434</v>
       </c>
       <c r="D67" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">-A67*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7523,8 +7611,8 @@
         <v>0</v>
       </c>
       <c r="D68" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">-A68*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7543,8 +7631,8 @@
         <v>-0.748843443462434</v>
       </c>
       <c r="D69" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">-A69*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7563,8 +7651,8 @@
         <v>-1.4816904659495</v>
       </c>
       <c r="D70" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">-A70*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7583,8 +7671,8 @@
         <v>-2.19748635838589</v>
       </c>
       <c r="D71" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">-A71*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7603,8 +7691,8 @@
         <v>-2.8953521965422</v>
       </c>
       <c r="D72" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">-A72*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7623,8 +7711,8 @@
         <v>-3.57370591680547</v>
       </c>
       <c r="D73" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">-A73*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7643,8 +7731,8 @@
         <v>-4.23131702525452</v>
       </c>
       <c r="D74" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">-A74*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7663,8 +7751,8 @@
         <v>-4.86625188858464</v>
       </c>
       <c r="D75" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">-A75*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7683,8 +7771,8 @@
         <v>-5.47675265833699</v>
       </c>
       <c r="D76" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">-A76*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7703,8 +7791,8 @@
         <v>-6.06088570120687</v>
       </c>
       <c r="D77" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">-A77*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7723,8 +7811,8 @@
         <v>-6.61671738388955</v>
       </c>
       <c r="D78" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">-A78*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7743,8 +7831,8 @@
         <v>-7.14231407308032</v>
       </c>
       <c r="D79" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">-A79*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7763,8 +7851,8 @@
         <v>-7.63556635062858</v>
       </c>
       <c r="D80" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">-A80*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7783,8 +7871,8 @@
         <v>-8.0947163680755</v>
       </c>
       <c r="D81" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">-A81*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7803,8 +7891,8 @@
         <v>-8.51800627696225</v>
       </c>
       <c r="D82" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">-A82*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7823,8 +7911,8 @@
         <v>-8.90367822882999</v>
       </c>
       <c r="D83" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">-A83*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7843,8 +7931,8 @@
         <v>-9.25067751460343</v>
       </c>
       <c r="D84" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">-A84*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7863,8 +7951,8 @@
         <v>-9.55777364036138</v>
       </c>
       <c r="D85" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">-A85*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7883,8 +7971,8 @@
         <v>-9.82391189702854</v>
       </c>
       <c r="D86" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">-A86*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7903,8 +7991,8 @@
         <v>-10.0485649300673</v>
       </c>
       <c r="D87" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">-A87*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7923,8 +8011,8 @@
         <v>-10.2315569546317</v>
       </c>
       <c r="D88" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">-A88*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7943,8 +8031,8 @@
         <v>-10.3727121858759</v>
       </c>
       <c r="D89" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">-A89*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7963,8 +8051,8 @@
         <v>-10.4725579783376</v>
       </c>
       <c r="D90" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">-A90*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7983,8 +8071,8 @@
         <v>-10.5312701168625</v>
       </c>
       <c r="D91" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">-A91*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8003,8 +8091,8 @@
         <v>-10.550079095372</v>
       </c>
       <c r="D92" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">-A92*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8023,8 +8111,8 @@
         <v>-10.5300396229414</v>
       </c>
       <c r="D93" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">-A93*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8043,8 +8131,8 @@
         <v>-10.4723821934917</v>
       </c>
       <c r="D94" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">-A94*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8063,8 +8151,8 @@
         <v>-10.3786888706359</v>
       </c>
       <c r="D95" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">-A95*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8083,8 +8171,8 @@
         <v>-10.250717502833</v>
       </c>
       <c r="D96" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">-A96*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8103,8 +8191,8 @@
         <v>-10.0905775082334</v>
       </c>
       <c r="D97" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">-A97*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8123,8 +8211,8 @@
         <v>-9.90020252014185</v>
       </c>
       <c r="D98" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">-A98*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8143,8 +8231,8 @@
         <v>-9.68170195670903</v>
       </c>
       <c r="D99" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">-A99*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8163,8 +8251,8 @@
         <v>-9.43736102093138</v>
       </c>
       <c r="D100" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">-A100*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8183,8 +8271,8 @@
         <v>-9.1692891309595</v>
       </c>
       <c r="D101" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">-A101*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8203,8 +8291,8 @@
         <v>-8.87994727463576</v>
       </c>
       <c r="D102" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">-A102*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8223,8 +8311,8 @@
         <v>-8.57162065495662</v>
       </c>
       <c r="D103" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">-A103*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8243,8 +8331,8 @@
         <v>-8.2464186900727</v>
       </c>
       <c r="D104" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">-A104*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8263,8 +8351,8 @@
         <v>-7.90680236782636</v>
       </c>
       <c r="D105" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">-A105*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8283,8 +8371,8 @@
         <v>-7.55488110636819</v>
       </c>
       <c r="D106" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">-A106*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8303,8 +8391,8 @@
         <v>-7.19258853900292</v>
       </c>
       <c r="D107" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">-A107*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8323,8 +8411,8 @@
         <v>-6.82238565357289</v>
       </c>
       <c r="D108" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">-A108*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8343,8 +8431,8 @@
         <v>-6.44603029853696</v>
       </c>
       <c r="D109" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">-A109*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8363,8 +8451,8 @@
         <v>-6.06563189204572</v>
       </c>
       <c r="D110" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">-A110*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8383,8 +8471,8 @@
         <v>-5.68294828255799</v>
       </c>
       <c r="D111" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">-A111*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8403,8 +8491,8 @@
         <v>-5.30026467307026</v>
       </c>
       <c r="D112" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">-A112*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8423,8 +8511,8 @@
         <v>-4.9189873423496</v>
       </c>
       <c r="D113" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">-A113*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8443,8 +8531,8 @@
         <v>-4.5412257085466</v>
       </c>
       <c r="D114" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">-A114*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8463,8 +8551,8 @@
         <v>-4.16856183527422</v>
       </c>
       <c r="D115" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">-A115*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8483,8 +8571,8 @@
         <v>-3.80310514068304</v>
       </c>
       <c r="D116" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">-A116*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8503,8 +8591,8 @@
         <v>-3.44626190354015</v>
       </c>
       <c r="D117" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">-A117*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8523,8 +8611,8 @@
         <v>-3.09996575715024</v>
       </c>
       <c r="D118" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">-A118*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8543,8 +8631,8 @@
         <v>-2.76597454997216</v>
       </c>
       <c r="D119" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">-A119*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8563,8 +8651,8 @@
         <v>-2.44587034561885</v>
       </c>
       <c r="D120" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">-A120*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8583,8 +8671,8 @@
         <v>-2.14141099254915</v>
       </c>
       <c r="D121" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">-A121*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8603,8 +8691,8 @@
         <v>-1.85435433922188</v>
       </c>
       <c r="D122" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">-A122*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8623,8 +8711,8 @@
         <v>-1.58593087955824</v>
       </c>
       <c r="D123" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">-A123*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8643,8 +8731,8 @@
         <v>-1.33789846201704</v>
       </c>
       <c r="D124" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">-A124*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8663,8 +8751,8 @@
         <v>-1.11166336536536</v>
       </c>
       <c r="D125" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">-A125*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8683,8 +8771,8 @@
         <v>-0.908631868370263</v>
       </c>
       <c r="D126" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">-A126*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8703,8 +8791,8 @@
         <v>-0.729858680107049</v>
       </c>
       <c r="D127" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">-A127*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8723,8 +8811,8 @@
         <v>-0.576574294496898</v>
       </c>
       <c r="D128" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">-A128*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8743,8 +8831,8 @@
         <v>-0.450009205460993</v>
       </c>
       <c r="D129" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">-A129*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8763,8 +8851,8 @@
         <v>-0.350514982691102</v>
       </c>
       <c r="D130" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">-A130*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8783,8 +8871,8 @@
         <v>-0.278970550416639</v>
       </c>
       <c r="D131" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">-A131*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8803,8 +8891,8 @@
         <v>-0.235903263175255</v>
       </c>
       <c r="D132" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">-A132*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8823,8 +8911,8 @@
         <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>35.78915</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>60.78915</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">-A133*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8847,17 +8935,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>93.1659683180963</v>
@@ -8877,37 +8965,43 @@
       <c r="K1" s="3" t="n">
         <v>35.78915</v>
       </c>
+      <c r="L1" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8922,15 +9016,15 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">-A3*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1003.5888666786</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
+      <c r="N3" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,15 +9039,15 @@
         <v>0.125028729482885</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">-A4*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1003.5344577531</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
+      <c r="N4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8968,8 +9062,8 @@
         <v>0.147854391720819</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">-A5*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8988,8 +9082,8 @@
         <v>0.185772940826284</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">-A6*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9008,8 +9102,8 @@
         <v>0.238504878894326</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">-A7*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9028,8 +9122,8 @@
         <v>0.305584376083356</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">-A8*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9048,8 +9142,8 @@
         <v>0.386825100456736</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">-A9*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9068,8 +9162,8 @@
         <v>0.48157489023624</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">-A10*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9088,8 +9182,8 @@
         <v>0.589181583643641</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">-A11*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9108,8 +9202,8 @@
         <v>0.709086184869031</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">-A12*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9128,8 +9222,8 @@
         <v>0.840543366165865</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">-A13*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9148,8 +9242,8 @@
         <v>0.982807799787598</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">-A14*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9168,8 +9262,8 @@
         <v>1.13494782605105</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">-A15*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9188,8 +9282,8 @@
         <v>1.29631128317799</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">-A16*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9208,8 +9302,8 @@
         <v>1.46596651148524</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">-A17*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9228,8 +9322,8 @@
         <v>1.64298185128963</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">-A18*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9248,8 +9342,8 @@
         <v>1.82651880887628</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">-A19*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9268,8 +9362,8 @@
         <v>2.01564572456201</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">-A20*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9288,8 +9382,8 @@
         <v>2.20933777269534</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">-A21*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9308,8 +9402,8 @@
         <v>2.4068496255297</v>
       </c>
       <c r="D22" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">-A22*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9328,8 +9422,8 @@
         <v>2.60706329144529</v>
       </c>
       <c r="D23" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">-A23*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9348,8 +9442,8 @@
         <v>2.80914027672724</v>
       </c>
       <c r="D24" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">-A24*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9368,8 +9462,8 @@
         <v>3.01196258975573</v>
       </c>
       <c r="D25" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">-A25*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9388,8 +9482,8 @@
         <v>3.21478490278423</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">-A26*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9408,8 +9502,8 @@
         <v>3.41639605822459</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">-A27*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9428,8 +9522,8 @@
         <v>3.61586439639363</v>
       </c>
       <c r="D28" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">-A28*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9448,8 +9542,8 @@
         <v>3.81207192567155</v>
       </c>
       <c r="D29" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">-A29*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9468,8 +9562,8 @@
         <v>4.00408698637514</v>
       </c>
       <c r="D30" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">-A30*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9488,8 +9582,8 @@
         <v>4.19060525494797</v>
       </c>
       <c r="D31" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">-A31*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9508,8 +9602,8 @@
         <v>4.37060190573853</v>
       </c>
       <c r="D32" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">-A32*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9528,8 +9622,8 @@
         <v>4.54295894712701</v>
       </c>
       <c r="D33" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">-A33*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9548,8 +9642,8 @@
         <v>4.70637205555695</v>
       </c>
       <c r="D34" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">-A34*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9568,8 +9662,8 @@
         <v>4.85972323940854</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">-A35*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9588,8 +9682,8 @@
         <v>5.00180134109364</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">-A36*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9608,8 +9702,8 @@
         <v>5.13130203705579</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">-A37*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9628,8 +9722,8 @@
         <v>5.24710733567518</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">-A38*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9648,8 +9742,8 @@
         <v>5.34800607936368</v>
       </c>
       <c r="D39" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">-A39*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9668,8 +9762,8 @@
         <v>5.43288027650147</v>
       </c>
       <c r="D40" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">-A40*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9688,8 +9782,8 @@
         <v>5.50070510143704</v>
       </c>
       <c r="D41" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">-A41*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9708,8 +9802,8 @@
         <v>5.55036256255059</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">-A42*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9728,8 +9822,8 @@
         <v>5.58092100015892</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">-A43*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9748,8 +9842,8 @@
         <v>5.59154192054719</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">-A44*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9768,8 +9862,8 @@
         <v>5.58157316193715</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">-A45*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9788,8 +9882,8 @@
         <v>5.5504557285189</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">-A46*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9808,8 +9902,8 @@
         <v>5.49753745851423</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">-A47*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9828,8 +9922,8 @@
         <v>5.42272518595479</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">-A48*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9848,8 +9942,8 @@
         <v>5.32573941293566</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">-A49*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9868,8 +9962,8 @@
         <v>5.20667330542513</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">-A50*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9888,8 +9982,8 @@
         <v>5.06562002939153</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">-A51*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9908,8 +10002,8 @@
         <v>4.90285908273982</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">-A52*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9928,8 +10022,8 @@
         <v>4.7189494612799</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">-A53*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9948,8 +10042,8 @@
         <v>4.51454332678999</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">-A54*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9968,8 +10062,8 @@
         <v>4.29019967508002</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">-A55*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9988,8 +10082,8 @@
         <v>4.04685016583315</v>
       </c>
       <c r="D56" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">-A56*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10008,8 +10102,8 @@
         <v>3.78542645873257</v>
       </c>
       <c r="D57" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">-A57*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10028,8 +10122,8 @@
         <v>3.50686021346146</v>
       </c>
       <c r="D58" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">-A58*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10048,8 +10142,8 @@
         <v>3.21226942163964</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">-A59*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10068,8 +10162,8 @@
         <v>2.90267890891861</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">-A60*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10088,8 +10182,8 @@
         <v>2.57911350094986</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">-A61*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10108,8 +10202,8 @@
         <v>2.2425980233849</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">-A62*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10128,8 +10222,8 @@
         <v>1.8940641359069</v>
       </c>
       <c r="D63" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">-A63*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10148,8 +10242,8 @@
         <v>1.53453666416736</v>
       </c>
       <c r="D64" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">-A64*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10168,8 +10262,8 @@
         <v>1.16466776994452</v>
       </c>
       <c r="D65" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">-A65*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10188,8 +10282,8 @@
         <v>0.785295946953234</v>
       </c>
       <c r="D66" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">-A66*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10208,8 +10302,8 @@
         <v>0.39688702503509</v>
       </c>
       <c r="D67" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">-A67*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10228,8 +10322,8 @@
         <v>0</v>
       </c>
       <c r="D68" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">-A68*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10248,8 +10342,8 @@
         <v>-0.39688702503509</v>
       </c>
       <c r="D69" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">-A69*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10268,8 +10362,8 @@
         <v>-0.785295946953234</v>
       </c>
       <c r="D70" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">-A70*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10288,8 +10382,8 @@
         <v>-1.16466776994452</v>
       </c>
       <c r="D71" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">-A71*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10308,8 +10402,8 @@
         <v>-1.53453666416736</v>
       </c>
       <c r="D72" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">-A72*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10328,8 +10422,8 @@
         <v>-1.8940641359069</v>
       </c>
       <c r="D73" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">-A73*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10348,8 +10442,8 @@
         <v>-2.2425980233849</v>
       </c>
       <c r="D74" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">-A74*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10368,8 +10462,8 @@
         <v>-2.57911350094986</v>
       </c>
       <c r="D75" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">-A75*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10388,8 +10482,8 @@
         <v>-2.90267890891861</v>
       </c>
       <c r="D76" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">-A76*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10408,8 +10502,8 @@
         <v>-3.21226942163964</v>
       </c>
       <c r="D77" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">-A77*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10428,8 +10522,8 @@
         <v>-3.50686021346146</v>
       </c>
       <c r="D78" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">-A78*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10448,8 +10542,8 @@
         <v>-3.78542645873257</v>
       </c>
       <c r="D79" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">-A79*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10468,8 +10562,8 @@
         <v>-4.04685016583315</v>
       </c>
       <c r="D80" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">-A80*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10488,8 +10582,8 @@
         <v>-4.29019967508002</v>
       </c>
       <c r="D81" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">-A81*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10508,8 +10602,8 @@
         <v>-4.51454332678999</v>
       </c>
       <c r="D82" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">-A82*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10528,8 +10622,8 @@
         <v>-4.7189494612799</v>
       </c>
       <c r="D83" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">-A83*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10548,8 +10642,8 @@
         <v>-4.90285908273982</v>
       </c>
       <c r="D84" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">-A84*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10568,8 +10662,8 @@
         <v>-5.06562002939153</v>
       </c>
       <c r="D85" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">-A85*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10588,8 +10682,8 @@
         <v>-5.20667330542513</v>
       </c>
       <c r="D86" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">-A86*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10608,8 +10702,8 @@
         <v>-5.32573941293566</v>
       </c>
       <c r="D87" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">-A87*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10628,8 +10722,8 @@
         <v>-5.42272518595479</v>
       </c>
       <c r="D88" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">-A88*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10648,8 +10742,8 @@
         <v>-5.49753745851423</v>
       </c>
       <c r="D89" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">-A89*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10668,8 +10762,8 @@
         <v>-5.5504557285189</v>
       </c>
       <c r="D90" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">-A90*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10688,8 +10782,8 @@
         <v>-5.58157316193715</v>
       </c>
       <c r="D91" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">-A91*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10708,8 +10802,8 @@
         <v>-5.59154192054719</v>
       </c>
       <c r="D92" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">-A92*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10728,8 +10822,8 @@
         <v>-5.58092100015892</v>
       </c>
       <c r="D93" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">-A93*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10748,8 +10842,8 @@
         <v>-5.55036256255059</v>
       </c>
       <c r="D94" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">-A94*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10768,8 +10862,8 @@
         <v>-5.50070510143704</v>
       </c>
       <c r="D95" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">-A95*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10788,8 +10882,8 @@
         <v>-5.43288027650147</v>
       </c>
       <c r="D96" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">-A96*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10808,8 +10902,8 @@
         <v>-5.34800607936368</v>
       </c>
       <c r="D97" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">-A97*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10828,8 +10922,8 @@
         <v>-5.24710733567518</v>
       </c>
       <c r="D98" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">-A98*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10848,8 +10942,8 @@
         <v>-5.13130203705579</v>
       </c>
       <c r="D99" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">-A99*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10868,8 +10962,8 @@
         <v>-5.00180134109364</v>
       </c>
       <c r="D100" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">-A100*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10888,8 +10982,8 @@
         <v>-4.85972323940854</v>
       </c>
       <c r="D101" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">-A101*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10908,8 +11002,8 @@
         <v>-4.70637205555695</v>
       </c>
       <c r="D102" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">-A102*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10928,8 +11022,8 @@
         <v>-4.54295894712701</v>
       </c>
       <c r="D103" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">-A103*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10948,8 +11042,8 @@
         <v>-4.37060190573853</v>
       </c>
       <c r="D104" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">-A104*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10968,8 +11062,8 @@
         <v>-4.19060525494797</v>
       </c>
       <c r="D105" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">-A105*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10988,8 +11082,8 @@
         <v>-4.00408698637514</v>
       </c>
       <c r="D106" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">-A106*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11008,8 +11102,8 @@
         <v>-3.81207192567155</v>
       </c>
       <c r="D107" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">-A107*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11028,8 +11122,8 @@
         <v>-3.61586439639363</v>
       </c>
       <c r="D108" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">-A108*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11048,8 +11142,8 @@
         <v>-3.41639605822459</v>
       </c>
       <c r="D109" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">-A109*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11068,8 +11162,8 @@
         <v>-3.21478490278423</v>
       </c>
       <c r="D110" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">-A110*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11088,8 +11182,8 @@
         <v>-3.01196258975573</v>
       </c>
       <c r="D111" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">-A111*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11108,8 +11202,8 @@
         <v>-2.80914027672724</v>
       </c>
       <c r="D112" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">-A112*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11128,8 +11222,8 @@
         <v>-2.60706329144529</v>
       </c>
       <c r="D113" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">-A113*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11148,8 +11242,8 @@
         <v>-2.4068496255297</v>
       </c>
       <c r="D114" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">-A114*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11168,8 +11262,8 @@
         <v>-2.20933777269534</v>
       </c>
       <c r="D115" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">-A115*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11188,8 +11282,8 @@
         <v>-2.01564572456201</v>
       </c>
       <c r="D116" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">-A116*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11208,8 +11302,8 @@
         <v>-1.82651880887628</v>
       </c>
       <c r="D117" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">-A117*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11228,8 +11322,8 @@
         <v>-1.64298185128963</v>
       </c>
       <c r="D118" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">-A118*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11248,8 +11342,8 @@
         <v>-1.46596651148524</v>
       </c>
       <c r="D119" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">-A119*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11268,8 +11362,8 @@
         <v>-1.29631128317799</v>
       </c>
       <c r="D120" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">-A120*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11288,8 +11382,8 @@
         <v>-1.13494782605105</v>
       </c>
       <c r="D121" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">-A121*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11308,8 +11402,8 @@
         <v>-0.982807799787598</v>
       </c>
       <c r="D122" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">-A122*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11328,8 +11422,8 @@
         <v>-0.840543366165865</v>
       </c>
       <c r="D123" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">-A123*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11348,8 +11442,8 @@
         <v>-0.709086184869031</v>
       </c>
       <c r="D124" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">-A124*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11368,8 +11462,8 @@
         <v>-0.589181583643641</v>
       </c>
       <c r="D125" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">-A125*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11388,8 +11482,8 @@
         <v>-0.48157489023624</v>
       </c>
       <c r="D126" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">-A126*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11408,8 +11502,8 @@
         <v>-0.386825100456736</v>
       </c>
       <c r="D127" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">-A127*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11428,8 +11522,8 @@
         <v>-0.305584376083356</v>
       </c>
       <c r="D128" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">-A128*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11448,8 +11542,8 @@
         <v>-0.238504878894326</v>
       </c>
       <c r="D129" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">-A129*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11468,8 +11562,8 @@
         <v>-0.185772940826284</v>
       </c>
       <c r="D130" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">-A130*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11488,8 +11582,8 @@
         <v>-0.147854391720819</v>
       </c>
       <c r="D131" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">-A131*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11508,8 +11602,8 @@
         <v>-0.125028729482885</v>
       </c>
       <c r="D132" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">-A132*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11528,8 +11622,8 @@
         <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <f aca="false">$G$1+$K$1</f>
-        <v>242.881276934999</v>
+        <f aca="false">$G$1+$K$1+$L$1</f>
+        <v>267.881276934999</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">-A133*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>

--- a/AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26.xlsx
+++ b/AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
   <si>
     <t xml:space="preserve">AIRCRAFT_EMPENNAGE_TRANSFORM_MICRO26 — SAE Aero 2026 Micro, guide §8.6</t>
   </si>
@@ -56,25 +56,40 @@
     <t xml:space="preserve">Trailing edge is CLOSED: B3 and B133 are overridden to 0 (the raw file carries ±0.00126).</t>
   </si>
   <si>
-    <t xml:space="preserve">L1 — THE EMPENNAGE VERTICAL DATUM</t>
+    <t xml:space="preserve">VERTICAL DATUM — K1 AND L1</t>
   </si>
   <si>
-    <t xml:space="preserve">The empennage is referenced to AX_Long_Emp, which sits y_emp_axis above AX_Long, so every sheet</t>
+    <t xml:space="preserve">The empennage is referenced to AX_Long_Emp, which sits y_emp_axis above AX_Long, so every sheet carries</t>
   </si>
   <si>
-    <t xml:space="preserve">carries L1 = y_emp_axis. For the HT this is its ONLY vertical datum — the stabiliser has none of its</t>
+    <t xml:space="preserve">L1 = y_emp_axis. Both root leading edges therefore land at the same height, Y = y_emp_axis. That is the</t>
   </si>
   <si>
-    <t xml:space="preserve">own, and its chord plane lands at Y = y_emp_axis. For the VT, L1 is applied ON TOP OF K1 = h_tail_top,</t>
+    <t xml:space="preserve">design intent — do not change L1 on one surface only.</t>
   </si>
   <si>
-    <t xml:space="preserve">which is itself measured from the waterline, so the fin root ends up h_tail_top above the boom axis.</t>
+    <t xml:space="preserve">K1 is the fin-root height measured FROM AX_Long_Emp, and it is 0: the fin roots on the boom axis. It is</t>
   </si>
   <si>
-    <t xml:space="preserve">If the fin should root ON the boom instead, set L1 to 0 on the two VT sheets and give the fin its own</t>
+    <t xml:space="preserve">NOT h_tail_top. h_tail_top is measured from the waterline; using it here would push the fin root above</t>
   </si>
   <si>
-    <t xml:space="preserve">y_VT_root global measured from AX_Long_Emp. Do not compensate by dropping L1 from the HT.</t>
+    <t xml:space="preserve">the HT root LE. K1 is the placeholder for a future y_VT_root global — if the fin ever needs to sit proud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the boom, add that global and read K1 from it rather than typing a number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNOWN INCONSISTENCY — h_VT_tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The equations file still defines h_VT_tip = h_tail_top + b_VT, which described the old waterline-seated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fin. With the fin on the boom axis the real fin-top height is y_emp_axis + b_VT = 232.092127.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_VT_tip currently reads 242.881277. Nothing in this workbook uses it; anything else that does is wrong.</t>
   </si>
   <si>
     <t xml:space="preserve">INCIDENCE SENSE — READ BEFORE CHANGING F1</t>
@@ -131,10 +146,10 @@
     <t xml:space="preserve">    x_VT_LE_root   = 848.292283</t>
   </si>
   <si>
-    <t xml:space="preserve">    h_tail_top     = 35.789150</t>
+    <t xml:space="preserve">    y_emp_axis     = 25.000000</t>
   </si>
   <si>
-    <t xml:space="preserve">    y_emp_axis     = 25.000000</t>
+    <t xml:space="preserve">    K1 fin-root seat = 0.000000   (not a global yet; see above)</t>
   </si>
   <si>
     <t xml:space="preserve">HT root — NACA 0012</t>
@@ -170,7 +185,7 @@
     <t xml:space="preserve">J1 root-LE station [mm]</t>
   </si>
   <si>
-    <t xml:space="preserve">L1 empennage lift [mm]</t>
+    <t xml:space="preserve">L1 empennage lift = y_emp_axis [mm]</t>
   </si>
   <si>
     <t xml:space="preserve">TE closed to 0 in B3 and B133 — see _README</t>
@@ -185,7 +200,7 @@
     <t xml:space="preserve">VT root — NACA 0012</t>
   </si>
   <si>
-    <t xml:space="preserve">K1 fin-root seat [mm]</t>
+    <t xml:space="preserve">K1 fin-root seat above AX_Long_Emp [mm]</t>
   </si>
   <si>
     <t xml:space="preserve">VT tip — NACA 0012</t>
@@ -580,7 +595,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="114"/>
@@ -681,15 +696,15 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="A22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -737,53 +752,81 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -807,12 +850,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>176.426266456864</v>
@@ -838,37 +882,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -891,7 +935,7 @@
         <v>-1024.47758847485</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -914,7 +958,7 @@
         <v>-1024.36635535396</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3518,12 +3562,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>176.426266456864</v>
@@ -3549,37 +3594,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3602,7 +3647,7 @@
         <v>-1024.47758847485</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3625,7 +3670,7 @@
         <v>-1024.36635535396</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6229,12 +6274,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>175.784845883201</v>
@@ -6252,7 +6298,7 @@
         <v>848.292282747392</v>
       </c>
       <c r="K1" s="3" t="n">
-        <v>35.78915</v>
+        <v>0</v>
       </c>
       <c r="L1" s="3" t="n">
         <v>25</v>
@@ -6260,37 +6306,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6306,14 +6352,14 @@
       </c>
       <c r="D3" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">-A3*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1024.07712863059</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6329,14 +6375,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">-A4*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1023.9744702806</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6352,7 +6398,7 @@
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">-A5*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6372,7 +6418,7 @@
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">-A6*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6392,7 +6438,7 @@
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">-A7*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6412,7 +6458,7 @@
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">-A8*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6432,7 +6478,7 @@
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">-A9*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6452,7 +6498,7 @@
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">-A10*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6472,7 +6518,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">-A11*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6492,7 +6538,7 @@
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">-A12*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6512,7 +6558,7 @@
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">-A13*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6532,7 +6578,7 @@
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">-A14*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6552,7 +6598,7 @@
       </c>
       <c r="D15" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">-A15*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6572,7 +6618,7 @@
       </c>
       <c r="D16" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">-A16*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6592,7 +6638,7 @@
       </c>
       <c r="D17" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">-A17*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6612,7 +6658,7 @@
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">-A18*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6632,7 +6678,7 @@
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">-A19*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6652,7 +6698,7 @@
       </c>
       <c r="D20" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">-A20*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6672,7 +6718,7 @@
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">-A21*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6692,7 +6738,7 @@
       </c>
       <c r="D22" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">-A22*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6712,7 +6758,7 @@
       </c>
       <c r="D23" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">-A23*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6732,7 +6778,7 @@
       </c>
       <c r="D24" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">-A24*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6752,7 +6798,7 @@
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">-A25*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6772,7 +6818,7 @@
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">-A26*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6792,7 +6838,7 @@
       </c>
       <c r="D27" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">-A27*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6812,7 +6858,7 @@
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">-A28*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6832,7 +6878,7 @@
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">-A29*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6852,7 +6898,7 @@
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">-A30*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6872,7 +6918,7 @@
       </c>
       <c r="D31" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">-A31*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6892,7 +6938,7 @@
       </c>
       <c r="D32" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">-A32*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6912,7 +6958,7 @@
       </c>
       <c r="D33" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">-A33*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6932,7 +6978,7 @@
       </c>
       <c r="D34" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">-A34*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6952,7 +6998,7 @@
       </c>
       <c r="D35" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">-A35*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6972,7 +7018,7 @@
       </c>
       <c r="D36" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">-A36*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -6992,7 +7038,7 @@
       </c>
       <c r="D37" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">-A37*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7012,7 +7058,7 @@
       </c>
       <c r="D38" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">-A38*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7032,7 +7078,7 @@
       </c>
       <c r="D39" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">-A39*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7052,7 +7098,7 @@
       </c>
       <c r="D40" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">-A40*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7072,7 +7118,7 @@
       </c>
       <c r="D41" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">-A41*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7092,7 +7138,7 @@
       </c>
       <c r="D42" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">-A42*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7112,7 +7158,7 @@
       </c>
       <c r="D43" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">-A43*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7132,7 +7178,7 @@
       </c>
       <c r="D44" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">-A44*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7152,7 +7198,7 @@
       </c>
       <c r="D45" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">-A45*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7172,7 +7218,7 @@
       </c>
       <c r="D46" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">-A46*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7192,7 +7238,7 @@
       </c>
       <c r="D47" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">-A47*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7212,7 +7258,7 @@
       </c>
       <c r="D48" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">-A48*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7232,7 +7278,7 @@
       </c>
       <c r="D49" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">-A49*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7252,7 +7298,7 @@
       </c>
       <c r="D50" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">-A50*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7272,7 +7318,7 @@
       </c>
       <c r="D51" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">-A51*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7292,7 +7338,7 @@
       </c>
       <c r="D52" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">-A52*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7312,7 +7358,7 @@
       </c>
       <c r="D53" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">-A53*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7332,7 +7378,7 @@
       </c>
       <c r="D54" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">-A54*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7352,7 +7398,7 @@
       </c>
       <c r="D55" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">-A55*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7372,7 +7418,7 @@
       </c>
       <c r="D56" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">-A56*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7392,7 +7438,7 @@
       </c>
       <c r="D57" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">-A57*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7412,7 +7458,7 @@
       </c>
       <c r="D58" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">-A58*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7432,7 +7478,7 @@
       </c>
       <c r="D59" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">-A59*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7452,7 +7498,7 @@
       </c>
       <c r="D60" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">-A60*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7472,7 +7518,7 @@
       </c>
       <c r="D61" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">-A61*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7492,7 +7538,7 @@
       </c>
       <c r="D62" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">-A62*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7512,7 +7558,7 @@
       </c>
       <c r="D63" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">-A63*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7532,7 +7578,7 @@
       </c>
       <c r="D64" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">-A64*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7552,7 +7598,7 @@
       </c>
       <c r="D65" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">-A65*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7572,7 +7618,7 @@
       </c>
       <c r="D66" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">-A66*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7592,7 +7638,7 @@
       </c>
       <c r="D67" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">-A67*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7612,7 +7658,7 @@
       </c>
       <c r="D68" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">-A68*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7632,7 +7678,7 @@
       </c>
       <c r="D69" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">-A69*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7652,7 +7698,7 @@
       </c>
       <c r="D70" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">-A70*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7672,7 +7718,7 @@
       </c>
       <c r="D71" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">-A71*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7692,7 +7738,7 @@
       </c>
       <c r="D72" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">-A72*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7712,7 +7758,7 @@
       </c>
       <c r="D73" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">-A73*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7732,7 +7778,7 @@
       </c>
       <c r="D74" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">-A74*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7752,7 +7798,7 @@
       </c>
       <c r="D75" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">-A75*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7772,7 +7818,7 @@
       </c>
       <c r="D76" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">-A76*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7792,7 +7838,7 @@
       </c>
       <c r="D77" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">-A77*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7812,7 +7858,7 @@
       </c>
       <c r="D78" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">-A78*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7832,7 +7878,7 @@
       </c>
       <c r="D79" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">-A79*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7852,7 +7898,7 @@
       </c>
       <c r="D80" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">-A80*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7872,7 +7918,7 @@
       </c>
       <c r="D81" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">-A81*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7892,7 +7938,7 @@
       </c>
       <c r="D82" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">-A82*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7912,7 +7958,7 @@
       </c>
       <c r="D83" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">-A83*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7932,7 +7978,7 @@
       </c>
       <c r="D84" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">-A84*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7952,7 +7998,7 @@
       </c>
       <c r="D85" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">-A85*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7972,7 +8018,7 @@
       </c>
       <c r="D86" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">-A86*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -7992,7 +8038,7 @@
       </c>
       <c r="D87" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">-A87*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8012,7 +8058,7 @@
       </c>
       <c r="D88" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">-A88*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8032,7 +8078,7 @@
       </c>
       <c r="D89" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">-A89*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8052,7 +8098,7 @@
       </c>
       <c r="D90" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">-A90*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8072,7 +8118,7 @@
       </c>
       <c r="D91" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">-A91*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8092,7 +8138,7 @@
       </c>
       <c r="D92" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">-A92*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8112,7 +8158,7 @@
       </c>
       <c r="D93" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">-A93*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8132,7 +8178,7 @@
       </c>
       <c r="D94" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">-A94*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8152,7 +8198,7 @@
       </c>
       <c r="D95" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">-A95*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8172,7 +8218,7 @@
       </c>
       <c r="D96" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">-A96*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8192,7 +8238,7 @@
       </c>
       <c r="D97" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">-A97*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8212,7 +8258,7 @@
       </c>
       <c r="D98" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">-A98*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8232,7 +8278,7 @@
       </c>
       <c r="D99" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">-A99*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8252,7 +8298,7 @@
       </c>
       <c r="D100" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">-A100*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8272,7 +8318,7 @@
       </c>
       <c r="D101" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">-A101*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8292,7 +8338,7 @@
       </c>
       <c r="D102" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">-A102*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8312,7 +8358,7 @@
       </c>
       <c r="D103" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">-A103*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8332,7 +8378,7 @@
       </c>
       <c r="D104" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">-A104*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8352,7 +8398,7 @@
       </c>
       <c r="D105" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">-A105*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8372,7 +8418,7 @@
       </c>
       <c r="D106" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">-A106*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8392,7 +8438,7 @@
       </c>
       <c r="D107" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">-A107*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8412,7 +8458,7 @@
       </c>
       <c r="D108" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">-A108*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8432,7 +8478,7 @@
       </c>
       <c r="D109" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">-A109*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8452,7 +8498,7 @@
       </c>
       <c r="D110" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">-A110*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8472,7 +8518,7 @@
       </c>
       <c r="D111" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">-A111*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8492,7 +8538,7 @@
       </c>
       <c r="D112" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">-A112*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8512,7 +8558,7 @@
       </c>
       <c r="D113" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">-A113*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8532,7 +8578,7 @@
       </c>
       <c r="D114" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">-A114*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8552,7 +8598,7 @@
       </c>
       <c r="D115" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">-A115*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8572,7 +8618,7 @@
       </c>
       <c r="D116" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">-A116*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8592,7 +8638,7 @@
       </c>
       <c r="D117" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">-A117*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8612,7 +8658,7 @@
       </c>
       <c r="D118" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">-A118*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8632,7 +8678,7 @@
       </c>
       <c r="D119" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">-A119*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8652,7 +8698,7 @@
       </c>
       <c r="D120" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">-A120*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8672,7 +8718,7 @@
       </c>
       <c r="D121" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">-A121*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8692,7 +8738,7 @@
       </c>
       <c r="D122" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">-A122*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8712,7 +8758,7 @@
       </c>
       <c r="D123" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">-A123*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8732,7 +8778,7 @@
       </c>
       <c r="D124" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">-A124*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8752,7 +8798,7 @@
       </c>
       <c r="D125" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">-A125*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8772,7 +8818,7 @@
       </c>
       <c r="D126" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">-A126*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8792,7 +8838,7 @@
       </c>
       <c r="D127" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">-A127*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8812,7 +8858,7 @@
       </c>
       <c r="D128" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">-A128*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8832,7 +8878,7 @@
       </c>
       <c r="D129" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">-A129*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8852,7 +8898,7 @@
       </c>
       <c r="D130" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">-A130*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8872,7 +8918,7 @@
       </c>
       <c r="D131" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">-A131*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8892,7 +8938,7 @@
       </c>
       <c r="D132" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">-A132*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8912,7 +8958,7 @@
       </c>
       <c r="D133" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>60.78915</v>
+        <v>25</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">-A133*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -8940,12 +8986,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>93.1659683180963</v>
@@ -8963,7 +9010,7 @@
         <v>848.292282747392</v>
       </c>
       <c r="K1" s="3" t="n">
-        <v>35.78915</v>
+        <v>0</v>
       </c>
       <c r="L1" s="3" t="n">
         <v>25</v>
@@ -8971,37 +9018,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9017,14 +9064,14 @@
       </c>
       <c r="D3" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">-A3*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1003.5888666786</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9040,14 +9087,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">-A4*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
         <v>-1003.5344577531</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9063,7 +9110,7 @@
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">-A5*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9083,7 +9130,7 @@
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">-A6*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9103,7 +9150,7 @@
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">-A7*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9123,7 +9170,7 @@
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">-A8*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9143,7 +9190,7 @@
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">-A9*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9163,7 +9210,7 @@
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">-A10*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9183,7 +9230,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">-A11*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9203,7 +9250,7 @@
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">-A12*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9223,7 +9270,7 @@
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">-A13*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9243,7 +9290,7 @@
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">-A14*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9263,7 +9310,7 @@
       </c>
       <c r="D15" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">-A15*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9283,7 +9330,7 @@
       </c>
       <c r="D16" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">-A16*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9303,7 +9350,7 @@
       </c>
       <c r="D17" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">-A17*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9323,7 +9370,7 @@
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">-A18*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9343,7 +9390,7 @@
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">-A19*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9363,7 +9410,7 @@
       </c>
       <c r="D20" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">-A20*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9383,7 +9430,7 @@
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">-A21*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9403,7 +9450,7 @@
       </c>
       <c r="D22" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">-A22*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9423,7 +9470,7 @@
       </c>
       <c r="D23" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">-A23*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9443,7 +9490,7 @@
       </c>
       <c r="D24" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">-A24*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9463,7 +9510,7 @@
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">-A25*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9483,7 +9530,7 @@
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">-A26*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9503,7 +9550,7 @@
       </c>
       <c r="D27" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">-A27*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9523,7 +9570,7 @@
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">-A28*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9543,7 +9590,7 @@
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">-A29*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9563,7 +9610,7 @@
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">-A30*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9583,7 +9630,7 @@
       </c>
       <c r="D31" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">-A31*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9603,7 +9650,7 @@
       </c>
       <c r="D32" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">-A32*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9623,7 +9670,7 @@
       </c>
       <c r="D33" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">-A33*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9643,7 +9690,7 @@
       </c>
       <c r="D34" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">-A34*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9663,7 +9710,7 @@
       </c>
       <c r="D35" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">-A35*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9683,7 +9730,7 @@
       </c>
       <c r="D36" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">-A36*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9703,7 +9750,7 @@
       </c>
       <c r="D37" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">-A37*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9723,7 +9770,7 @@
       </c>
       <c r="D38" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">-A38*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9743,7 +9790,7 @@
       </c>
       <c r="D39" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">-A39*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9763,7 +9810,7 @@
       </c>
       <c r="D40" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">-A40*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9783,7 +9830,7 @@
       </c>
       <c r="D41" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">-A41*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9803,7 +9850,7 @@
       </c>
       <c r="D42" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">-A42*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9823,7 +9870,7 @@
       </c>
       <c r="D43" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">-A43*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9843,7 +9890,7 @@
       </c>
       <c r="D44" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">-A44*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9863,7 +9910,7 @@
       </c>
       <c r="D45" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">-A45*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9883,7 +9930,7 @@
       </c>
       <c r="D46" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">-A46*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9903,7 +9950,7 @@
       </c>
       <c r="D47" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">-A47*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9923,7 +9970,7 @@
       </c>
       <c r="D48" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">-A48*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9943,7 +9990,7 @@
       </c>
       <c r="D49" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">-A49*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9963,7 +10010,7 @@
       </c>
       <c r="D50" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">-A50*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -9983,7 +10030,7 @@
       </c>
       <c r="D51" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">-A51*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10003,7 +10050,7 @@
       </c>
       <c r="D52" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">-A52*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10023,7 +10070,7 @@
       </c>
       <c r="D53" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">-A53*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10043,7 +10090,7 @@
       </c>
       <c r="D54" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">-A54*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10063,7 +10110,7 @@
       </c>
       <c r="D55" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">-A55*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10083,7 +10130,7 @@
       </c>
       <c r="D56" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">-A56*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10103,7 +10150,7 @@
       </c>
       <c r="D57" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">-A57*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10123,7 +10170,7 @@
       </c>
       <c r="D58" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">-A58*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10143,7 +10190,7 @@
       </c>
       <c r="D59" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">-A59*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10163,7 +10210,7 @@
       </c>
       <c r="D60" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">-A60*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10183,7 +10230,7 @@
       </c>
       <c r="D61" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">-A61*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10203,7 +10250,7 @@
       </c>
       <c r="D62" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">-A62*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10223,7 +10270,7 @@
       </c>
       <c r="D63" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">-A63*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10243,7 +10290,7 @@
       </c>
       <c r="D64" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">-A64*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10263,7 +10310,7 @@
       </c>
       <c r="D65" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">-A65*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10283,7 +10330,7 @@
       </c>
       <c r="D66" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">-A66*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10303,7 +10350,7 @@
       </c>
       <c r="D67" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">-A67*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10323,7 +10370,7 @@
       </c>
       <c r="D68" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E68" s="5" t="n">
         <f aca="false">-A68*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10343,7 +10390,7 @@
       </c>
       <c r="D69" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E69" s="5" t="n">
         <f aca="false">-A69*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10363,7 +10410,7 @@
       </c>
       <c r="D70" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E70" s="5" t="n">
         <f aca="false">-A70*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10383,7 +10430,7 @@
       </c>
       <c r="D71" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E71" s="5" t="n">
         <f aca="false">-A71*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10403,7 +10450,7 @@
       </c>
       <c r="D72" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E72" s="5" t="n">
         <f aca="false">-A72*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10423,7 +10470,7 @@
       </c>
       <c r="D73" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E73" s="5" t="n">
         <f aca="false">-A73*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10443,7 +10490,7 @@
       </c>
       <c r="D74" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E74" s="5" t="n">
         <f aca="false">-A74*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10463,7 +10510,7 @@
       </c>
       <c r="D75" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E75" s="5" t="n">
         <f aca="false">-A75*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10483,7 +10530,7 @@
       </c>
       <c r="D76" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E76" s="5" t="n">
         <f aca="false">-A76*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10503,7 +10550,7 @@
       </c>
       <c r="D77" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E77" s="5" t="n">
         <f aca="false">-A77*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10523,7 +10570,7 @@
       </c>
       <c r="D78" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E78" s="5" t="n">
         <f aca="false">-A78*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10543,7 +10590,7 @@
       </c>
       <c r="D79" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E79" s="5" t="n">
         <f aca="false">-A79*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10563,7 +10610,7 @@
       </c>
       <c r="D80" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E80" s="5" t="n">
         <f aca="false">-A80*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10583,7 +10630,7 @@
       </c>
       <c r="D81" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E81" s="5" t="n">
         <f aca="false">-A81*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10603,7 +10650,7 @@
       </c>
       <c r="D82" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E82" s="5" t="n">
         <f aca="false">-A82*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10623,7 +10670,7 @@
       </c>
       <c r="D83" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E83" s="5" t="n">
         <f aca="false">-A83*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10643,7 +10690,7 @@
       </c>
       <c r="D84" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E84" s="5" t="n">
         <f aca="false">-A84*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10663,7 +10710,7 @@
       </c>
       <c r="D85" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E85" s="5" t="n">
         <f aca="false">-A85*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10683,7 +10730,7 @@
       </c>
       <c r="D86" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E86" s="5" t="n">
         <f aca="false">-A86*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10703,7 +10750,7 @@
       </c>
       <c r="D87" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E87" s="5" t="n">
         <f aca="false">-A87*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10723,7 +10770,7 @@
       </c>
       <c r="D88" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E88" s="5" t="n">
         <f aca="false">-A88*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10743,7 +10790,7 @@
       </c>
       <c r="D89" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E89" s="5" t="n">
         <f aca="false">-A89*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10763,7 +10810,7 @@
       </c>
       <c r="D90" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E90" s="5" t="n">
         <f aca="false">-A90*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10783,7 +10830,7 @@
       </c>
       <c r="D91" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E91" s="5" t="n">
         <f aca="false">-A91*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10803,7 +10850,7 @@
       </c>
       <c r="D92" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E92" s="5" t="n">
         <f aca="false">-A92*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10823,7 +10870,7 @@
       </c>
       <c r="D93" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E93" s="5" t="n">
         <f aca="false">-A93*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10843,7 +10890,7 @@
       </c>
       <c r="D94" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E94" s="5" t="n">
         <f aca="false">-A94*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10863,7 +10910,7 @@
       </c>
       <c r="D95" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E95" s="5" t="n">
         <f aca="false">-A95*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10883,7 +10930,7 @@
       </c>
       <c r="D96" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E96" s="5" t="n">
         <f aca="false">-A96*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10903,7 +10950,7 @@
       </c>
       <c r="D97" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E97" s="5" t="n">
         <f aca="false">-A97*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10923,7 +10970,7 @@
       </c>
       <c r="D98" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E98" s="5" t="n">
         <f aca="false">-A98*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10943,7 +10990,7 @@
       </c>
       <c r="D99" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E99" s="5" t="n">
         <f aca="false">-A99*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10963,7 +11010,7 @@
       </c>
       <c r="D100" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E100" s="5" t="n">
         <f aca="false">-A100*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -10983,7 +11030,7 @@
       </c>
       <c r="D101" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E101" s="5" t="n">
         <f aca="false">-A101*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11003,7 +11050,7 @@
       </c>
       <c r="D102" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E102" s="5" t="n">
         <f aca="false">-A102*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11023,7 +11070,7 @@
       </c>
       <c r="D103" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E103" s="5" t="n">
         <f aca="false">-A103*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11043,7 +11090,7 @@
       </c>
       <c r="D104" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E104" s="5" t="n">
         <f aca="false">-A104*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11063,7 +11110,7 @@
       </c>
       <c r="D105" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E105" s="5" t="n">
         <f aca="false">-A105*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11083,7 +11130,7 @@
       </c>
       <c r="D106" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">-A106*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11103,7 +11150,7 @@
       </c>
       <c r="D107" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E107" s="5" t="n">
         <f aca="false">-A107*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11123,7 +11170,7 @@
       </c>
       <c r="D108" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E108" s="5" t="n">
         <f aca="false">-A108*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11143,7 +11190,7 @@
       </c>
       <c r="D109" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E109" s="5" t="n">
         <f aca="false">-A109*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11163,7 +11210,7 @@
       </c>
       <c r="D110" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E110" s="5" t="n">
         <f aca="false">-A110*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11183,7 +11230,7 @@
       </c>
       <c r="D111" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E111" s="5" t="n">
         <f aca="false">-A111*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11203,7 +11250,7 @@
       </c>
       <c r="D112" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E112" s="5" t="n">
         <f aca="false">-A112*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11223,7 +11270,7 @@
       </c>
       <c r="D113" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">-A113*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11243,7 +11290,7 @@
       </c>
       <c r="D114" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E114" s="5" t="n">
         <f aca="false">-A114*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11263,7 +11310,7 @@
       </c>
       <c r="D115" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E115" s="5" t="n">
         <f aca="false">-A115*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11283,7 +11330,7 @@
       </c>
       <c r="D116" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">-A116*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11303,7 +11350,7 @@
       </c>
       <c r="D117" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">-A117*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11323,7 +11370,7 @@
       </c>
       <c r="D118" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E118" s="5" t="n">
         <f aca="false">-A118*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11343,7 +11390,7 @@
       </c>
       <c r="D119" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E119" s="5" t="n">
         <f aca="false">-A119*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11363,7 +11410,7 @@
       </c>
       <c r="D120" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E120" s="5" t="n">
         <f aca="false">-A120*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11383,7 +11430,7 @@
       </c>
       <c r="D121" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E121" s="5" t="n">
         <f aca="false">-A121*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11403,7 +11450,7 @@
       </c>
       <c r="D122" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E122" s="5" t="n">
         <f aca="false">-A122*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11423,7 +11470,7 @@
       </c>
       <c r="D123" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E123" s="5" t="n">
         <f aca="false">-A123*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11443,7 +11490,7 @@
       </c>
       <c r="D124" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E124" s="5" t="n">
         <f aca="false">-A124*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11463,7 +11510,7 @@
       </c>
       <c r="D125" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E125" s="5" t="n">
         <f aca="false">-A125*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11483,7 +11530,7 @@
       </c>
       <c r="D126" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E126" s="5" t="n">
         <f aca="false">-A126*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11503,7 +11550,7 @@
       </c>
       <c r="D127" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E127" s="5" t="n">
         <f aca="false">-A127*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11523,7 +11570,7 @@
       </c>
       <c r="D128" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E128" s="5" t="n">
         <f aca="false">-A128*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11543,7 +11590,7 @@
       </c>
       <c r="D129" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E129" s="5" t="n">
         <f aca="false">-A129*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11563,7 +11610,7 @@
       </c>
       <c r="D130" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E130" s="5" t="n">
         <f aca="false">-A130*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11583,7 +11630,7 @@
       </c>
       <c r="D131" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E131" s="5" t="n">
         <f aca="false">-A131*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11603,7 +11650,7 @@
       </c>
       <c r="D132" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E132" s="5" t="n">
         <f aca="false">-A132*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
@@ -11623,7 +11670,7 @@
       </c>
       <c r="D133" s="5" t="n">
         <f aca="false">$G$1+$K$1+$L$1</f>
-        <v>267.881276934999</v>
+        <v>232.092126934999</v>
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">-A133*$E$1-($G$1*TAN(RADIANS($H$1)))-$J$1</f>
